--- a/docs/ZIPBODA_API 및 인터페이스 정의서_v0.1.xlsx
+++ b/docs/ZIPBODA_API 및 인터페이스 정의서_v0.1.xlsx
@@ -849,11 +849,23 @@
       <c r="F5" s="21" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="50">
-      <c r="A6" s="21" t="n"/>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="24" t="n"/>
+      <c r="A6" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>Figma 정합 2차 — 쇼룸/방문예약(API-050~052·140~143) 제거(집구경=인테리어 영감으로 통합), 관리자 연관화면을 통합 프레임으로 갱신(회원&amp;커뮤니티 MEMBER-01·알림&amp;통계 NOTI-01·시스템&amp;감사 SYS-01·상품 SHOP-01·연계 SUBS-01), 통합검색(095) 연관화면 COM-01, 커뮤니티 글수정(063)·비밀번호 재설정(006) 연관화면 반영, 영감 관리 명칭 집구경 반영</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="n"/>
-      <c r="E6" s="30" t="n"/>
+      <c r="E6" s="30" t="n">
+        <v>46234</v>
+      </c>
       <c r="F6" s="21" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="50">
@@ -1908,7 +1920,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U91"/>
+  <dimension ref="A1:U84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.13" customWidth="1" style="50" min="1" max="1"/>
@@ -2754,7 +2766,7 @@
       </c>
       <c r="S9" s="47" t="inlineStr">
         <is>
-          <t>ZB-U-AUTH-03</t>
+          <t>ZB-U-AUTH-03, ZB-U-AUTH-04</t>
         </is>
       </c>
       <c r="T9" s="47" t="inlineStr"/>
@@ -4464,22 +4476,22 @@
     <row r="26" s="50">
       <c r="A26" s="47" t="inlineStr">
         <is>
-          <t>API-050</t>
+          <t>API-060</t>
         </is>
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>쇼룸</t>
+          <t>커뮤니티</t>
         </is>
       </c>
       <c r="C26" s="42" t="inlineStr">
         <is>
-          <t>/api/showrooms</t>
+          <t>/api/community/posts</t>
         </is>
       </c>
       <c r="D26" s="43" t="inlineStr">
         <is>
-          <t>쇼룸 목록/지도</t>
+          <t>게시글 목록</t>
         </is>
       </c>
       <c r="E26" s="44" t="inlineStr">
@@ -4525,320 +4537,10 @@
       </c>
       <c r="M26" s="45" t="inlineStr">
         <is>
-          <t>?bounds=(bbox)</t>
+          <t>?category=(string)&amp;sort=(string)&amp;page=(int)</t>
         </is>
       </c>
       <c r="N26" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "success": (boolean),
-  "data": (object|null),
-  "error": (object|null)
-}
-data: { "items": [ { "id","name","address","lat","lng","open","distance","reviews" } ] }</t>
-        </is>
-      </c>
-      <c r="O26" s="45" t="inlineStr">
-        <is>
-          <t>영업상태·거리</t>
-        </is>
-      </c>
-      <c r="P26" s="46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q26" s="47" t="inlineStr"/>
-      <c r="R26" s="47" t="inlineStr">
-        <is>
-          <t>ERR-007</t>
-        </is>
-      </c>
-      <c r="S26" s="47" t="inlineStr">
-        <is>
-          <t>ZB-U-SHOW-01</t>
-        </is>
-      </c>
-      <c r="T26" s="47" t="inlineStr"/>
-      <c r="U26" s="48" t="n">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="27" s="50">
-      <c r="A27" s="47" t="inlineStr">
-        <is>
-          <t>API-051</t>
-        </is>
-      </c>
-      <c r="B27" s="41" t="inlineStr">
-        <is>
-          <t>쇼룸</t>
-        </is>
-      </c>
-      <c r="C27" s="42" t="inlineStr">
-        <is>
-          <t>/api/showrooms/{id}</t>
-        </is>
-      </c>
-      <c r="D27" s="43" t="inlineStr">
-        <is>
-          <t>쇼룸 상세</t>
-        </is>
-      </c>
-      <c r="E27" s="44" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F27" s="44" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G27" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H27" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I27" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J27" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K27" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json</t>
-        </is>
-      </c>
-      <c r="L27" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Date: (표준)</t>
-        </is>
-      </c>
-      <c r="M27" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "success": (boolean),
-  "data": (object|null),
-  "error": (object|null)
-}
-data: { "id","name","hours","products":[],"slots":[] }</t>
-        </is>
-      </c>
-      <c r="O27" s="45" t="inlineStr">
-        <is>
-          <t>예약 슬롯</t>
-        </is>
-      </c>
-      <c r="P27" s="46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q27" s="47" t="inlineStr"/>
-      <c r="R27" s="47" t="inlineStr">
-        <is>
-          <t>ERR-008</t>
-        </is>
-      </c>
-      <c r="S27" s="47" t="inlineStr">
-        <is>
-          <t>ZB-U-SHOW-02</t>
-        </is>
-      </c>
-      <c r="T27" s="47" t="inlineStr"/>
-      <c r="U27" s="48" t="n">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="28" s="50">
-      <c r="A28" s="47" t="inlineStr">
-        <is>
-          <t>API-052</t>
-        </is>
-      </c>
-      <c r="B28" s="41" t="inlineStr">
-        <is>
-          <t>쇼룸</t>
-        </is>
-      </c>
-      <c r="C28" s="42" t="inlineStr">
-        <is>
-          <t>/api/showrooms/{id}/reservations</t>
-        </is>
-      </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>방문 예약</t>
-        </is>
-      </c>
-      <c r="E28" s="44" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F28" s="44" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G28" s="44" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H28" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I28" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J28" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K28" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Authorization: Bearer {accessToken}</t>
-        </is>
-      </c>
-      <c r="L28" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Date: (표준)</t>
-        </is>
-      </c>
-      <c r="M28" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "date*": (string),
-  "time*": (string),
-  "people*": (int)
-}</t>
-        </is>
-      </c>
-      <c r="N28" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "success": (boolean),
-  "data": (object|null),
-  "error": (object|null)
-}
-data: { "reservationId": (string) }</t>
-        </is>
-      </c>
-      <c r="O28" s="45" t="inlineStr"/>
-      <c r="P28" s="46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q28" s="47" t="inlineStr"/>
-      <c r="R28" s="47" t="inlineStr">
-        <is>
-          <t>ERR-003,ERR-009</t>
-        </is>
-      </c>
-      <c r="S28" s="47" t="inlineStr">
-        <is>
-          <t>ZB-U-SHOW-02</t>
-        </is>
-      </c>
-      <c r="T28" s="47" t="inlineStr"/>
-      <c r="U28" s="48" t="n">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="29" s="50">
-      <c r="A29" s="47" t="inlineStr">
-        <is>
-          <t>API-060</t>
-        </is>
-      </c>
-      <c r="B29" s="41" t="inlineStr">
-        <is>
-          <t>커뮤니티</t>
-        </is>
-      </c>
-      <c r="C29" s="42" t="inlineStr">
-        <is>
-          <t>/api/community/posts</t>
-        </is>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>게시글 목록</t>
-        </is>
-      </c>
-      <c r="E29" s="44" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F29" s="44" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G29" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H29" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I29" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J29" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K29" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json</t>
-        </is>
-      </c>
-      <c r="L29" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Date: (표준)</t>
-        </is>
-      </c>
-      <c r="M29" s="45" t="inlineStr">
-        <is>
-          <t>?category=(string)&amp;sort=(string)&amp;page=(int)</t>
-        </is>
-      </c>
-      <c r="N29" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -4848,104 +4550,104 @@
 data: { "items": [ { "id","category","title","author","likes","comments","thumbnail" } ], "page","totalCount" }</t>
         </is>
       </c>
-      <c r="O29" s="45" t="inlineStr">
+      <c r="O26" s="45" t="inlineStr">
         <is>
           <t>카테고리 필터</t>
         </is>
       </c>
-      <c r="P29" s="46" t="inlineStr">
+      <c r="P26" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q29" s="47" t="inlineStr">
+      <c r="Q26" s="47" t="inlineStr">
         <is>
           <t>ITF-008,ITF-010</t>
         </is>
       </c>
-      <c r="R29" s="47" t="inlineStr">
+      <c r="R26" s="47" t="inlineStr">
         <is>
           <t>ERR-007</t>
         </is>
       </c>
-      <c r="S29" s="47" t="inlineStr">
+      <c r="S26" s="47" t="inlineStr">
         <is>
           <t>ZB-U-COMM-01</t>
         </is>
       </c>
-      <c r="T29" s="47" t="inlineStr"/>
-      <c r="U29" s="48" t="n">
+      <c r="T26" s="47" t="inlineStr"/>
+      <c r="U26" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="30" s="50">
-      <c r="A30" s="47" t="inlineStr">
+    <row r="27" s="50">
+      <c r="A27" s="47" t="inlineStr">
         <is>
           <t>API-061</t>
         </is>
       </c>
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C30" s="42" t="inlineStr">
+      <c r="C27" s="42" t="inlineStr">
         <is>
           <t>/api/community/posts/{id}</t>
         </is>
       </c>
-      <c r="D30" s="43" t="inlineStr">
+      <c r="D27" s="43" t="inlineStr">
         <is>
           <t>게시글 상세</t>
         </is>
       </c>
-      <c r="E30" s="44" t="inlineStr">
+      <c r="E27" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F30" s="44" t="inlineStr">
+      <c r="F27" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G30" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H30" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I30" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J30" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K30" s="45" t="inlineStr">
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I27" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J27" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json</t>
         </is>
       </c>
-      <c r="L30" s="45" t="inlineStr">
+      <c r="L27" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M30" s="45" t="inlineStr">
+      <c r="M27" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N30" s="45" t="inlineStr">
+      <c r="N27" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -4955,92 +4657,92 @@
 data: { "id","title","content","images":[],"likes","comments":[] }</t>
         </is>
       </c>
-      <c r="O30" s="45" t="inlineStr"/>
-      <c r="P30" s="46" t="inlineStr">
+      <c r="O27" s="45" t="inlineStr"/>
+      <c r="P27" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q30" s="47" t="inlineStr"/>
-      <c r="R30" s="47" t="inlineStr">
+      <c r="Q27" s="47" t="inlineStr"/>
+      <c r="R27" s="47" t="inlineStr">
         <is>
           <t>ERR-008</t>
         </is>
       </c>
-      <c r="S30" s="47" t="inlineStr">
+      <c r="S27" s="47" t="inlineStr">
         <is>
           <t>ZB-U-COMM-02</t>
         </is>
       </c>
-      <c r="T30" s="47" t="inlineStr"/>
-      <c r="U30" s="48" t="n">
+      <c r="T27" s="47" t="inlineStr"/>
+      <c r="U27" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="31" s="50">
-      <c r="A31" s="47" t="inlineStr">
+    <row r="28" s="50">
+      <c r="A28" s="47" t="inlineStr">
         <is>
           <t>API-062</t>
         </is>
       </c>
-      <c r="B31" s="41" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C31" s="42" t="inlineStr">
+      <c r="C28" s="42" t="inlineStr">
         <is>
           <t>/api/community/posts</t>
         </is>
       </c>
-      <c r="D31" s="43" t="inlineStr">
+      <c r="D28" s="43" t="inlineStr">
         <is>
           <t>게시글 작성</t>
         </is>
       </c>
-      <c r="E31" s="44" t="inlineStr">
+      <c r="E28" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F31" s="44" t="inlineStr">
+      <c r="F28" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G31" s="44" t="inlineStr">
+      <c r="G28" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H31" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I31" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J31" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K31" s="45" t="inlineStr">
+      <c r="H28" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I28" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L31" s="45" t="inlineStr">
+      <c r="L28" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M31" s="45" t="inlineStr">
+      <c r="M28" s="45" t="inlineStr">
         <is>
           <t>{
   "category*": (string),
@@ -5050,7 +4752,7 @@
 }</t>
         </is>
       </c>
-      <c r="N31" s="45" t="inlineStr">
+      <c r="N28" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -5060,103 +4762,103 @@
 data: { "postId": (string) }</t>
         </is>
       </c>
-      <c r="O31" s="45" t="inlineStr"/>
-      <c r="P31" s="46" t="inlineStr">
+      <c r="O28" s="45" t="inlineStr"/>
+      <c r="P28" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q31" s="47" t="inlineStr">
+      <c r="Q28" s="47" t="inlineStr">
         <is>
           <t>ITF-008</t>
         </is>
       </c>
-      <c r="R31" s="47" t="inlineStr">
+      <c r="R28" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005</t>
         </is>
       </c>
-      <c r="S31" s="47" t="inlineStr">
+      <c r="S28" s="47" t="inlineStr">
         <is>
           <t>ZB-U-COMM-03</t>
         </is>
       </c>
-      <c r="T31" s="47" t="inlineStr"/>
-      <c r="U31" s="48" t="n">
+      <c r="T28" s="47" t="inlineStr"/>
+      <c r="U28" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="32" s="50">
-      <c r="A32" s="47" t="inlineStr">
+    <row r="29" s="50">
+      <c r="A29" s="47" t="inlineStr">
         <is>
           <t>API-063</t>
         </is>
       </c>
-      <c r="B32" s="41" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C32" s="42" t="inlineStr">
+      <c r="C29" s="42" t="inlineStr">
         <is>
           <t>/api/community/posts/{id}</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>게시글 수정</t>
         </is>
       </c>
-      <c r="E32" s="44" t="inlineStr">
+      <c r="E29" s="44" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F32" s="44" t="inlineStr">
+      <c r="F29" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G32" s="44" t="inlineStr">
+      <c r="G29" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H32" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I32" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J32" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K32" s="45" t="inlineStr">
+      <c r="H29" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I29" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L32" s="45" t="inlineStr">
+      <c r="L29" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M32" s="45" t="inlineStr">
+      <c r="M29" s="45" t="inlineStr">
         <is>
           <t>{
   "title","content","images":[]
 }</t>
         </is>
       </c>
-      <c r="N32" s="45" t="inlineStr">
+      <c r="N29" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -5165,101 +4867,101 @@
 }</t>
         </is>
       </c>
-      <c r="O32" s="45" t="inlineStr">
+      <c r="O29" s="45" t="inlineStr">
         <is>
           <t>작성자만</t>
         </is>
       </c>
-      <c r="P32" s="46" t="inlineStr">
+      <c r="P29" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q32" s="47" t="inlineStr"/>
-      <c r="R32" s="47" t="inlineStr">
+      <c r="Q29" s="47" t="inlineStr"/>
+      <c r="R29" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-013</t>
         </is>
       </c>
-      <c r="S32" s="47" t="inlineStr">
-        <is>
-          <t>ZB-U-COMM-02</t>
-        </is>
-      </c>
-      <c r="T32" s="47" t="inlineStr"/>
-      <c r="U32" s="48" t="n">
+      <c r="S29" s="47" t="inlineStr">
+        <is>
+          <t>ZB-U-COMM-04</t>
+        </is>
+      </c>
+      <c r="T29" s="47" t="inlineStr"/>
+      <c r="U29" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="33" s="50">
-      <c r="A33" s="47" t="inlineStr">
+    <row r="30" s="50">
+      <c r="A30" s="47" t="inlineStr">
         <is>
           <t>API-064</t>
         </is>
       </c>
-      <c r="B33" s="41" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C33" s="42" t="inlineStr">
+      <c r="C30" s="42" t="inlineStr">
         <is>
           <t>/api/community/posts/{id}</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
+      <c r="D30" s="43" t="inlineStr">
         <is>
           <t>게시글 삭제</t>
         </is>
       </c>
-      <c r="E33" s="44" t="inlineStr">
+      <c r="E30" s="44" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="F33" s="44" t="inlineStr">
+      <c r="F30" s="44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G33" s="44" t="inlineStr">
+      <c r="G30" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H33" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I33" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J33" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K33" s="45" t="inlineStr">
+      <c r="H30" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I30" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L33" s="45" t="inlineStr">
+      <c r="L30" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M33" s="45" t="inlineStr">
+      <c r="M30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N33" s="45" t="inlineStr">
+      <c r="N30" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -5268,103 +4970,103 @@
 }</t>
         </is>
       </c>
-      <c r="O33" s="45" t="inlineStr">
+      <c r="O30" s="45" t="inlineStr">
         <is>
           <t>작성자/운영자</t>
         </is>
       </c>
-      <c r="P33" s="46" t="inlineStr">
+      <c r="P30" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q33" s="47" t="inlineStr"/>
-      <c r="R33" s="47" t="inlineStr">
+      <c r="Q30" s="47" t="inlineStr"/>
+      <c r="R30" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-013</t>
         </is>
       </c>
-      <c r="S33" s="47" t="inlineStr">
+      <c r="S30" s="47" t="inlineStr">
         <is>
           <t>ZB-U-COMM-02</t>
         </is>
       </c>
-      <c r="T33" s="47" t="inlineStr"/>
-      <c r="U33" s="48" t="n">
+      <c r="T30" s="47" t="inlineStr"/>
+      <c r="U30" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="34" s="50">
-      <c r="A34" s="47" t="inlineStr">
+    <row r="31" s="50">
+      <c r="A31" s="47" t="inlineStr">
         <is>
           <t>API-065</t>
         </is>
       </c>
-      <c r="B34" s="41" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C34" s="42" t="inlineStr">
+      <c r="C31" s="42" t="inlineStr">
         <is>
           <t>/api/community/posts/{id}/comments</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
+      <c r="D31" s="43" t="inlineStr">
         <is>
           <t>댓글 작성</t>
         </is>
       </c>
-      <c r="E34" s="44" t="inlineStr">
+      <c r="E31" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F34" s="44" t="inlineStr">
+      <c r="F31" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G34" s="44" t="inlineStr">
+      <c r="G31" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H34" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I34" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J34" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K34" s="45" t="inlineStr">
+      <c r="H31" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I31" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L34" s="45" t="inlineStr">
+      <c r="L31" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M34" s="45" t="inlineStr">
+      <c r="M31" s="45" t="inlineStr">
         <is>
           <t>{
   "content*": (string)
 }</t>
         </is>
       </c>
-      <c r="N34" s="45" t="inlineStr">
+      <c r="N31" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -5373,99 +5075,99 @@
 }</t>
         </is>
       </c>
-      <c r="O34" s="45" t="inlineStr"/>
-      <c r="P34" s="46" t="inlineStr">
+      <c r="O31" s="45" t="inlineStr"/>
+      <c r="P31" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q34" s="47" t="inlineStr"/>
-      <c r="R34" s="47" t="inlineStr">
+      <c r="Q31" s="47" t="inlineStr"/>
+      <c r="R31" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S34" s="47" t="inlineStr">
+      <c r="S31" s="47" t="inlineStr">
         <is>
           <t>ZB-U-COMM-02</t>
         </is>
       </c>
-      <c r="T34" s="47" t="inlineStr"/>
-      <c r="U34" s="48" t="n">
+      <c r="T31" s="47" t="inlineStr"/>
+      <c r="U31" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="35" s="50">
-      <c r="A35" s="47" t="inlineStr">
+    <row r="32" s="50">
+      <c r="A32" s="47" t="inlineStr">
         <is>
           <t>API-066</t>
         </is>
       </c>
-      <c r="B35" s="41" t="inlineStr">
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C35" s="42" t="inlineStr">
+      <c r="C32" s="42" t="inlineStr">
         <is>
           <t>/api/community/posts/{id}/like</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
+      <c r="D32" s="43" t="inlineStr">
         <is>
           <t>좋아요 토글</t>
         </is>
       </c>
-      <c r="E35" s="44" t="inlineStr">
+      <c r="E32" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F35" s="44" t="inlineStr">
+      <c r="F32" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G35" s="44" t="inlineStr">
+      <c r="G32" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H35" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I35" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J35" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K35" s="45" t="inlineStr">
+      <c r="H32" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I32" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J32" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L35" s="45" t="inlineStr">
+      <c r="L32" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M35" s="45" t="inlineStr">
+      <c r="M32" s="45" t="inlineStr">
         <is>
           <t>{
   "liked*": (boolean)
 }</t>
         </is>
       </c>
-      <c r="N35" s="45" t="inlineStr">
+      <c r="N32" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -5474,96 +5176,96 @@
 }</t>
         </is>
       </c>
-      <c r="O35" s="45" t="inlineStr"/>
-      <c r="P35" s="46" t="inlineStr">
+      <c r="O32" s="45" t="inlineStr"/>
+      <c r="P32" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q35" s="47" t="inlineStr"/>
-      <c r="R35" s="47" t="inlineStr">
+      <c r="Q32" s="47" t="inlineStr"/>
+      <c r="R32" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S35" s="47" t="inlineStr">
+      <c r="S32" s="47" t="inlineStr">
         <is>
           <t>ZB-U-COMM-02</t>
         </is>
       </c>
-      <c r="T35" s="47" t="inlineStr"/>
-      <c r="U35" s="48" t="n">
+      <c r="T32" s="47" t="inlineStr"/>
+      <c r="U32" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="36" s="50">
-      <c r="A36" s="47" t="inlineStr">
+    <row r="33" s="50">
+      <c r="A33" s="47" t="inlineStr">
         <is>
           <t>API-070</t>
         </is>
       </c>
-      <c r="B36" s="41" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C36" s="42" t="inlineStr">
+      <c r="C33" s="42" t="inlineStr">
         <is>
           <t>/api/products</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr">
+      <c r="D33" s="43" t="inlineStr">
         <is>
           <t>가구 상품 목록</t>
         </is>
       </c>
-      <c r="E36" s="44" t="inlineStr">
+      <c r="E33" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F36" s="44" t="inlineStr">
+      <c r="F33" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G36" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H36" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I36" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J36" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K36" s="45" t="inlineStr">
+      <c r="G33" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H33" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I33" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J33" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json</t>
         </is>
       </c>
-      <c r="L36" s="45" t="inlineStr">
+      <c r="L33" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M36" s="45" t="inlineStr">
+      <c r="M33" s="45" t="inlineStr">
         <is>
           <t>?category=(string)&amp;discount=(int)&amp;sort=(string)&amp;page=(int)</t>
         </is>
       </c>
-      <c r="N36" s="45" t="inlineStr">
+      <c r="N33" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -5573,108 +5275,108 @@
 data: { "items": [ { "id","brand","name","price","originalPrice","discount","rating","reviews" } ], "page","totalCount" }</t>
         </is>
       </c>
-      <c r="O36" s="45" t="inlineStr">
+      <c r="O33" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P36" s="46" t="inlineStr">
+      <c r="P33" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q36" s="47" t="inlineStr">
+      <c r="Q33" s="47" t="inlineStr">
         <is>
           <t>ITF-007,ITF-010</t>
         </is>
       </c>
-      <c r="R36" s="47" t="inlineStr">
+      <c r="R33" s="47" t="inlineStr">
         <is>
           <t>ERR-007</t>
         </is>
       </c>
-      <c r="S36" s="47" t="inlineStr">
+      <c r="S33" s="47" t="inlineStr">
         <is>
           <t>ZB-U-SHOP-01</t>
         </is>
       </c>
-      <c r="T36" s="47" t="inlineStr">
+      <c r="T33" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U36" s="48" t="n">
+      <c r="U33" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="37" s="50">
-      <c r="A37" s="47" t="inlineStr">
+    <row r="34" s="50">
+      <c r="A34" s="47" t="inlineStr">
         <is>
           <t>API-071</t>
         </is>
       </c>
-      <c r="B37" s="41" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C37" s="42" t="inlineStr">
+      <c r="C34" s="42" t="inlineStr">
         <is>
           <t>/api/products/{id}</t>
         </is>
       </c>
-      <c r="D37" s="43" t="inlineStr">
+      <c r="D34" s="43" t="inlineStr">
         <is>
           <t>상품 상세</t>
         </is>
       </c>
-      <c r="E37" s="44" t="inlineStr">
+      <c r="E34" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F37" s="44" t="inlineStr">
+      <c r="F34" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G37" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H37" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I37" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J37" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K37" s="45" t="inlineStr">
+      <c r="G34" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H34" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I34" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json</t>
         </is>
       </c>
-      <c r="L37" s="45" t="inlineStr">
+      <c r="L34" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M37" s="45" t="inlineStr">
+      <c r="M34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N37" s="45" t="inlineStr">
+      <c r="N34" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -5684,105 +5386,105 @@
 data: { "id","brand","name","price","options":[],"dimensions":{},"reviews":[] }</t>
         </is>
       </c>
-      <c r="O37" s="45" t="inlineStr">
+      <c r="O34" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P37" s="46" t="inlineStr">
+      <c r="P34" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q37" s="47" t="inlineStr"/>
-      <c r="R37" s="47" t="inlineStr">
+      <c r="Q34" s="47" t="inlineStr"/>
+      <c r="R34" s="47" t="inlineStr">
         <is>
           <t>ERR-008</t>
         </is>
       </c>
-      <c r="S37" s="47" t="inlineStr">
+      <c r="S34" s="47" t="inlineStr">
         <is>
           <t>ZB-U-SHOP-02</t>
         </is>
       </c>
-      <c r="T37" s="47" t="inlineStr">
+      <c r="T34" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U37" s="48" t="n">
+      <c r="U34" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="38" s="50">
-      <c r="A38" s="47" t="inlineStr">
+    <row r="35" s="50">
+      <c r="A35" s="47" t="inlineStr">
         <is>
           <t>API-072</t>
         </is>
       </c>
-      <c r="B38" s="41" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C38" s="42" t="inlineStr">
+      <c r="C35" s="42" t="inlineStr">
         <is>
           <t>/api/cart</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
+      <c r="D35" s="43" t="inlineStr">
         <is>
           <t>장바구니 조회</t>
         </is>
       </c>
-      <c r="E38" s="44" t="inlineStr">
+      <c r="E35" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F38" s="44" t="inlineStr">
+      <c r="F35" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G38" s="44" t="inlineStr">
+      <c r="G35" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H38" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I38" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J38" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K38" s="45" t="inlineStr">
+      <c r="H35" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I35" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L38" s="45" t="inlineStr">
+      <c r="L35" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M38" s="45" t="inlineStr">
+      <c r="M35" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N38" s="45" t="inlineStr">
+      <c r="N35" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -5792,100 +5494,100 @@
 data: { "items":[], "totalPrice": (int) }</t>
         </is>
       </c>
-      <c r="O38" s="45" t="inlineStr">
+      <c r="O35" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P38" s="46" t="inlineStr">
+      <c r="P35" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q38" s="47" t="inlineStr"/>
-      <c r="R38" s="47" t="inlineStr">
+      <c r="Q35" s="47" t="inlineStr"/>
+      <c r="R35" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S38" s="47" t="inlineStr">
+      <c r="S35" s="47" t="inlineStr">
         <is>
           <t>ZB-U-CART-01</t>
         </is>
       </c>
-      <c r="T38" s="47" t="inlineStr">
+      <c r="T35" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U38" s="48" t="n">
+      <c r="U35" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="39" s="50">
-      <c r="A39" s="47" t="inlineStr">
+    <row r="36" s="50">
+      <c r="A36" s="47" t="inlineStr">
         <is>
           <t>API-073</t>
         </is>
       </c>
-      <c r="B39" s="41" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C39" s="42" t="inlineStr">
+      <c r="C36" s="42" t="inlineStr">
         <is>
           <t>/api/cart/items</t>
         </is>
       </c>
-      <c r="D39" s="43" t="inlineStr">
+      <c r="D36" s="43" t="inlineStr">
         <is>
           <t>장바구니 담기</t>
         </is>
       </c>
-      <c r="E39" s="44" t="inlineStr">
+      <c r="E36" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F39" s="44" t="inlineStr">
+      <c r="F36" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G39" s="44" t="inlineStr">
+      <c r="G36" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H39" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I39" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J39" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K39" s="45" t="inlineStr">
+      <c r="H36" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I36" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L39" s="45" t="inlineStr">
+      <c r="L36" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M39" s="45" t="inlineStr">
+      <c r="M36" s="45" t="inlineStr">
         <is>
           <t>{
   "productId*": (string),
@@ -5894,7 +5596,7 @@
 }</t>
         </is>
       </c>
-      <c r="N39" s="45" t="inlineStr">
+      <c r="N36" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -5903,107 +5605,107 @@
 }</t>
         </is>
       </c>
-      <c r="O39" s="45" t="inlineStr">
+      <c r="O36" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P39" s="46" t="inlineStr">
+      <c r="P36" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q39" s="47" t="inlineStr"/>
-      <c r="R39" s="47" t="inlineStr">
+      <c r="Q36" s="47" t="inlineStr"/>
+      <c r="R36" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005</t>
         </is>
       </c>
-      <c r="S39" s="47" t="inlineStr">
+      <c r="S36" s="47" t="inlineStr">
         <is>
           <t>ZB-U-CART-01</t>
         </is>
       </c>
-      <c r="T39" s="47" t="inlineStr">
+      <c r="T36" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U39" s="48" t="n">
+      <c r="U36" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="40" s="50">
-      <c r="A40" s="47" t="inlineStr">
+    <row r="37" s="50">
+      <c r="A37" s="47" t="inlineStr">
         <is>
           <t>API-074</t>
         </is>
       </c>
-      <c r="B40" s="41" t="inlineStr">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C40" s="42" t="inlineStr">
+      <c r="C37" s="42" t="inlineStr">
         <is>
           <t>/api/cart/items/{id}</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
+      <c r="D37" s="43" t="inlineStr">
         <is>
           <t>수량 변경</t>
         </is>
       </c>
-      <c r="E40" s="44" t="inlineStr">
+      <c r="E37" s="44" t="inlineStr">
         <is>
           <t>PATCH</t>
         </is>
       </c>
-      <c r="F40" s="44" t="inlineStr">
+      <c r="F37" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G40" s="44" t="inlineStr">
+      <c r="G37" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H40" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I40" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J40" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K40" s="45" t="inlineStr">
+      <c r="H37" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I37" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J37" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L40" s="45" t="inlineStr">
+      <c r="L37" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M40" s="45" t="inlineStr">
+      <c r="M37" s="45" t="inlineStr">
         <is>
           <t>{
   "quantity*": (int)
 }</t>
         </is>
       </c>
-      <c r="N40" s="45" t="inlineStr">
+      <c r="N37" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -6012,105 +5714,105 @@
 }</t>
         </is>
       </c>
-      <c r="O40" s="45" t="inlineStr">
+      <c r="O37" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P40" s="46" t="inlineStr">
+      <c r="P37" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q40" s="47" t="inlineStr"/>
-      <c r="R40" s="47" t="inlineStr">
+      <c r="Q37" s="47" t="inlineStr"/>
+      <c r="R37" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S40" s="47" t="inlineStr">
+      <c r="S37" s="47" t="inlineStr">
         <is>
           <t>ZB-U-CART-01</t>
         </is>
       </c>
-      <c r="T40" s="47" t="inlineStr">
+      <c r="T37" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U40" s="48" t="n">
+      <c r="U37" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="41" s="50">
-      <c r="A41" s="47" t="inlineStr">
+    <row r="38" s="50">
+      <c r="A38" s="47" t="inlineStr">
         <is>
           <t>API-075</t>
         </is>
       </c>
-      <c r="B41" s="41" t="inlineStr">
+      <c r="B38" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C41" s="42" t="inlineStr">
+      <c r="C38" s="42" t="inlineStr">
         <is>
           <t>/api/cart/items/{id}</t>
         </is>
       </c>
-      <c r="D41" s="43" t="inlineStr">
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t>장바구니 삭제</t>
         </is>
       </c>
-      <c r="E41" s="44" t="inlineStr">
+      <c r="E38" s="44" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="F41" s="44" t="inlineStr">
+      <c r="F38" s="44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G41" s="44" t="inlineStr">
+      <c r="G38" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H41" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I41" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J41" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K41" s="45" t="inlineStr">
+      <c r="H38" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I38" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J38" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L41" s="45" t="inlineStr">
+      <c r="L38" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M41" s="45" t="inlineStr">
+      <c r="M38" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N41" s="45" t="inlineStr">
+      <c r="N38" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -6119,100 +5821,100 @@
 }</t>
         </is>
       </c>
-      <c r="O41" s="45" t="inlineStr">
+      <c r="O38" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P41" s="46" t="inlineStr">
+      <c r="P38" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q41" s="47" t="inlineStr"/>
-      <c r="R41" s="47" t="inlineStr">
+      <c r="Q38" s="47" t="inlineStr"/>
+      <c r="R38" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S41" s="47" t="inlineStr">
+      <c r="S38" s="47" t="inlineStr">
         <is>
           <t>ZB-U-CART-01</t>
         </is>
       </c>
-      <c r="T41" s="47" t="inlineStr">
+      <c r="T38" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U41" s="48" t="n">
+      <c r="U38" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="42" s="50">
-      <c r="A42" s="47" t="inlineStr">
+    <row r="39" s="50">
+      <c r="A39" s="47" t="inlineStr">
         <is>
           <t>API-076</t>
         </is>
       </c>
-      <c r="B42" s="41" t="inlineStr">
+      <c r="B39" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C42" s="42" t="inlineStr">
+      <c r="C39" s="42" t="inlineStr">
         <is>
           <t>/api/orders</t>
         </is>
       </c>
-      <c r="D42" s="43" t="inlineStr">
+      <c r="D39" s="43" t="inlineStr">
         <is>
           <t>주문/결제</t>
         </is>
       </c>
-      <c r="E42" s="44" t="inlineStr">
+      <c r="E39" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F42" s="44" t="inlineStr">
+      <c r="F39" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G42" s="44" t="inlineStr">
+      <c r="G39" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H42" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I42" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J42" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K42" s="45" t="inlineStr">
+      <c r="H39" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I39" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L42" s="45" t="inlineStr">
+      <c r="L39" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M42" s="45" t="inlineStr">
+      <c r="M39" s="45" t="inlineStr">
         <is>
           <t>{
   "items*": [ {"productId","quantity"} ],
@@ -6221,7 +5923,7 @@
 }</t>
         </is>
       </c>
-      <c r="N42" s="45" t="inlineStr">
+      <c r="N39" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -6231,109 +5933,109 @@
 data: { "orderId": (string), "status": (string) }</t>
         </is>
       </c>
-      <c r="O42" s="45" t="inlineStr">
+      <c r="O39" s="45" t="inlineStr">
         <is>
           <t>2차·재고 반영</t>
         </is>
       </c>
-      <c r="P42" s="46" t="inlineStr">
+      <c r="P39" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q42" s="47" t="inlineStr">
+      <c r="Q39" s="47" t="inlineStr">
         <is>
           <t>ITF-006</t>
         </is>
       </c>
-      <c r="R42" s="47" t="inlineStr">
+      <c r="R39" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005,ERR-014</t>
         </is>
       </c>
-      <c r="S42" s="47" t="inlineStr">
+      <c r="S39" s="47" t="inlineStr">
         <is>
           <t>ZB-U-CART-02,ZB-U-CART-03</t>
         </is>
       </c>
-      <c r="T42" s="47" t="inlineStr">
+      <c r="T39" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U42" s="48" t="n">
+      <c r="U39" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="43" s="50">
-      <c r="A43" s="47" t="inlineStr">
+    <row r="40" s="50">
+      <c r="A40" s="47" t="inlineStr">
         <is>
           <t>API-077</t>
         </is>
       </c>
-      <c r="B43" s="41" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C43" s="42" t="inlineStr">
+      <c r="C40" s="42" t="inlineStr">
         <is>
           <t>/api/orders</t>
         </is>
       </c>
-      <c r="D43" s="43" t="inlineStr">
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t>주문 목록</t>
         </is>
       </c>
-      <c r="E43" s="44" t="inlineStr">
+      <c r="E40" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F43" s="44" t="inlineStr">
+      <c r="F40" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G43" s="44" t="inlineStr">
+      <c r="G40" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H43" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I43" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J43" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K43" s="45" t="inlineStr">
+      <c r="H40" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I40" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J40" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L43" s="45" t="inlineStr">
+      <c r="L40" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M43" s="45" t="inlineStr">
+      <c r="M40" s="45" t="inlineStr">
         <is>
           <t>?page=(int)</t>
         </is>
       </c>
-      <c r="N43" s="45" t="inlineStr">
+      <c r="N40" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -6343,109 +6045,109 @@
 data: { "items":[ {"orderId","products","shippingStatus"} ] }</t>
         </is>
       </c>
-      <c r="O43" s="45" t="inlineStr">
+      <c r="O40" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P43" s="46" t="inlineStr">
+      <c r="P40" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q43" s="47" t="inlineStr">
+      <c r="Q40" s="47" t="inlineStr">
         <is>
           <t>ITF-006</t>
         </is>
       </c>
-      <c r="R43" s="47" t="inlineStr">
+      <c r="R40" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S43" s="47" t="inlineStr">
+      <c r="S40" s="47" t="inlineStr">
         <is>
           <t>ZB-U-MY-03</t>
         </is>
       </c>
-      <c r="T43" s="47" t="inlineStr">
+      <c r="T40" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U43" s="48" t="n">
+      <c r="U40" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="44" s="50">
-      <c r="A44" s="47" t="inlineStr">
+    <row r="41" s="50">
+      <c r="A41" s="47" t="inlineStr">
         <is>
           <t>API-078</t>
         </is>
       </c>
-      <c r="B44" s="41" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C44" s="42" t="inlineStr">
+      <c r="C41" s="42" t="inlineStr">
         <is>
           <t>/api/orders/{id}</t>
         </is>
       </c>
-      <c r="D44" s="43" t="inlineStr">
+      <c r="D41" s="43" t="inlineStr">
         <is>
           <t>주문 상세</t>
         </is>
       </c>
-      <c r="E44" s="44" t="inlineStr">
+      <c r="E41" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F44" s="44" t="inlineStr">
+      <c r="F41" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G44" s="44" t="inlineStr">
+      <c r="G41" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H44" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I44" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J44" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K44" s="45" t="inlineStr">
+      <c r="H41" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I41" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J41" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L44" s="45" t="inlineStr">
+      <c r="L41" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M44" s="45" t="inlineStr">
+      <c r="M41" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N44" s="45" t="inlineStr">
+      <c r="N41" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -6455,104 +6157,104 @@
 data: { "orderId","items","shipping","shippingStatus" }</t>
         </is>
       </c>
-      <c r="O44" s="45" t="inlineStr">
+      <c r="O41" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P44" s="46" t="inlineStr">
+      <c r="P41" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q44" s="47" t="inlineStr">
+      <c r="Q41" s="47" t="inlineStr">
         <is>
           <t>ITF-006</t>
         </is>
       </c>
-      <c r="R44" s="47" t="inlineStr">
+      <c r="R41" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S44" s="47" t="inlineStr">
+      <c r="S41" s="47" t="inlineStr">
         <is>
           <t>ZB-U-MY-03</t>
         </is>
       </c>
-      <c r="T44" s="47" t="inlineStr">
+      <c r="T41" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U44" s="48" t="n">
+      <c r="U41" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="45" s="50">
-      <c r="A45" s="47" t="inlineStr">
+    <row r="42" s="50">
+      <c r="A42" s="47" t="inlineStr">
         <is>
           <t>API-079</t>
         </is>
       </c>
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C45" s="42" t="inlineStr">
+      <c r="C42" s="42" t="inlineStr">
         <is>
           <t>/api/products/{id}/reviews</t>
         </is>
       </c>
-      <c r="D45" s="43" t="inlineStr">
+      <c r="D42" s="43" t="inlineStr">
         <is>
           <t>상품 리뷰 작성</t>
         </is>
       </c>
-      <c r="E45" s="44" t="inlineStr">
+      <c r="E42" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F45" s="44" t="inlineStr">
+      <c r="F42" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G45" s="44" t="inlineStr">
+      <c r="G42" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H45" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I45" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J45" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K45" s="45" t="inlineStr">
+      <c r="H42" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I42" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J42" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L45" s="45" t="inlineStr">
+      <c r="L42" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M45" s="45" t="inlineStr">
+      <c r="M42" s="45" t="inlineStr">
         <is>
           <t>{
   "rating*": (int),
@@ -6560,7 +6262,7 @@
 }</t>
         </is>
       </c>
-      <c r="N45" s="45" t="inlineStr">
+      <c r="N42" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -6569,107 +6271,107 @@
 }</t>
         </is>
       </c>
-      <c r="O45" s="45" t="inlineStr">
+      <c r="O42" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P45" s="46" t="inlineStr">
+      <c r="P42" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q45" s="47" t="inlineStr"/>
-      <c r="R45" s="47" t="inlineStr">
+      <c r="Q42" s="47" t="inlineStr"/>
+      <c r="R42" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005</t>
         </is>
       </c>
-      <c r="S45" s="47" t="inlineStr">
+      <c r="S42" s="47" t="inlineStr">
         <is>
           <t>ZB-U-SHOP-02</t>
         </is>
       </c>
-      <c r="T45" s="47" t="inlineStr">
+      <c r="T42" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U45" s="48" t="n">
+      <c r="U42" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="46" s="50">
-      <c r="A46" s="47" t="inlineStr">
+    <row r="43" s="50">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>API-080</t>
         </is>
       </c>
-      <c r="B46" s="41" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C46" s="42" t="inlineStr">
+      <c r="C43" s="42" t="inlineStr">
         <is>
           <t>/api/wishlist</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
+      <c r="D43" s="43" t="inlineStr">
         <is>
           <t>찜 추가</t>
         </is>
       </c>
-      <c r="E46" s="44" t="inlineStr">
+      <c r="E43" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F46" s="44" t="inlineStr">
+      <c r="F43" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G46" s="44" t="inlineStr">
+      <c r="G43" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H46" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I46" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J46" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K46" s="45" t="inlineStr">
+      <c r="H43" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I43" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J43" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L46" s="45" t="inlineStr">
+      <c r="L43" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M46" s="45" t="inlineStr">
+      <c r="M43" s="45" t="inlineStr">
         <is>
           <t>{
   "productId*": (string)
 }</t>
         </is>
       </c>
-      <c r="N46" s="45" t="inlineStr">
+      <c r="N43" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -6678,105 +6380,105 @@
 }</t>
         </is>
       </c>
-      <c r="O46" s="45" t="inlineStr">
+      <c r="O43" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P46" s="46" t="inlineStr">
+      <c r="P43" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q46" s="47" t="inlineStr"/>
-      <c r="R46" s="47" t="inlineStr">
+      <c r="Q43" s="47" t="inlineStr"/>
+      <c r="R43" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S46" s="47" t="inlineStr">
+      <c r="S43" s="47" t="inlineStr">
         <is>
           <t>ZB-U-MY-02</t>
         </is>
       </c>
-      <c r="T46" s="47" t="inlineStr">
+      <c r="T43" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U46" s="48" t="n">
+      <c r="U43" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="47" s="50">
-      <c r="A47" s="47" t="inlineStr">
+    <row r="44" s="50">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>API-081</t>
         </is>
       </c>
-      <c r="B47" s="41" t="inlineStr">
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C47" s="42" t="inlineStr">
+      <c r="C44" s="42" t="inlineStr">
         <is>
           <t>/api/wishlist</t>
         </is>
       </c>
-      <c r="D47" s="43" t="inlineStr">
+      <c r="D44" s="43" t="inlineStr">
         <is>
           <t>찜 목록</t>
         </is>
       </c>
-      <c r="E47" s="44" t="inlineStr">
+      <c r="E44" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F47" s="44" t="inlineStr">
+      <c r="F44" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G47" s="44" t="inlineStr">
+      <c r="G44" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H47" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I47" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J47" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K47" s="45" t="inlineStr">
+      <c r="H44" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I44" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L47" s="45" t="inlineStr">
+      <c r="L44" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M47" s="45" t="inlineStr">
+      <c r="M44" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N47" s="45" t="inlineStr">
+      <c r="N44" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -6786,105 +6488,105 @@
 data: { "items":[] }</t>
         </is>
       </c>
-      <c r="O47" s="45" t="inlineStr">
+      <c r="O44" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P47" s="46" t="inlineStr">
+      <c r="P44" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q47" s="47" t="inlineStr"/>
-      <c r="R47" s="47" t="inlineStr">
+      <c r="Q44" s="47" t="inlineStr"/>
+      <c r="R44" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S47" s="47" t="inlineStr">
+      <c r="S44" s="47" t="inlineStr">
         <is>
           <t>ZB-U-MY-02</t>
         </is>
       </c>
-      <c r="T47" s="47" t="inlineStr">
+      <c r="T44" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U47" s="48" t="n">
+      <c r="U44" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="48" s="50">
-      <c r="A48" s="47" t="inlineStr">
+    <row r="45" s="50">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>API-082</t>
         </is>
       </c>
-      <c r="B48" s="41" t="inlineStr">
+      <c r="B45" s="41" t="inlineStr">
         <is>
           <t>커머스</t>
         </is>
       </c>
-      <c r="C48" s="42" t="inlineStr">
+      <c r="C45" s="42" t="inlineStr">
         <is>
           <t>/api/wishlist/{id}</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
+      <c r="D45" s="43" t="inlineStr">
         <is>
           <t>찜 삭제</t>
         </is>
       </c>
-      <c r="E48" s="44" t="inlineStr">
+      <c r="E45" s="44" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="F48" s="44" t="inlineStr">
+      <c r="F45" s="44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G48" s="44" t="inlineStr">
+      <c r="G45" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H48" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I48" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J48" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K48" s="45" t="inlineStr">
+      <c r="H45" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I45" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J45" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L48" s="45" t="inlineStr">
+      <c r="L45" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M48" s="45" t="inlineStr">
+      <c r="M45" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N48" s="45" t="inlineStr">
+      <c r="N45" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -6893,105 +6595,105 @@
 }</t>
         </is>
       </c>
-      <c r="O48" s="45" t="inlineStr">
+      <c r="O45" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P48" s="46" t="inlineStr">
+      <c r="P45" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q48" s="47" t="inlineStr"/>
-      <c r="R48" s="47" t="inlineStr">
+      <c r="Q45" s="47" t="inlineStr"/>
+      <c r="R45" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S48" s="47" t="inlineStr">
+      <c r="S45" s="47" t="inlineStr">
         <is>
           <t>ZB-U-MY-02</t>
         </is>
       </c>
-      <c r="T48" s="47" t="inlineStr">
+      <c r="T45" s="47" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="U48" s="48" t="n">
+      <c r="U45" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="49" s="50">
-      <c r="A49" s="47" t="inlineStr">
+    <row r="46" s="50">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>API-090</t>
         </is>
       </c>
-      <c r="B49" s="41" t="inlineStr">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>마이</t>
         </is>
       </c>
-      <c r="C49" s="42" t="inlineStr">
+      <c r="C46" s="42" t="inlineStr">
         <is>
           <t>/api/me/profile</t>
         </is>
       </c>
-      <c r="D49" s="43" t="inlineStr">
+      <c r="D46" s="43" t="inlineStr">
         <is>
           <t>프로필 조회</t>
         </is>
       </c>
-      <c r="E49" s="44" t="inlineStr">
+      <c r="E46" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F49" s="44" t="inlineStr">
+      <c r="F46" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G49" s="44" t="inlineStr">
+      <c r="G46" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H49" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I49" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J49" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K49" s="45" t="inlineStr">
+      <c r="H46" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I46" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J46" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L49" s="45" t="inlineStr">
+      <c r="L46" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M49" s="45" t="inlineStr">
+      <c r="M46" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N49" s="45" t="inlineStr">
+      <c r="N46" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7001,99 +6703,99 @@
 data: { "name","email","phone","verified","notifications":{} }</t>
         </is>
       </c>
-      <c r="O49" s="45" t="inlineStr"/>
-      <c r="P49" s="46" t="inlineStr">
+      <c r="O46" s="45" t="inlineStr"/>
+      <c r="P46" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q49" s="47" t="inlineStr"/>
-      <c r="R49" s="47" t="inlineStr">
+      <c r="Q46" s="47" t="inlineStr"/>
+      <c r="R46" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S49" s="47" t="inlineStr">
+      <c r="S46" s="47" t="inlineStr">
         <is>
           <t>ZB-U-MY-04</t>
         </is>
       </c>
-      <c r="T49" s="47" t="inlineStr"/>
-      <c r="U49" s="48" t="n">
+      <c r="T46" s="47" t="inlineStr"/>
+      <c r="U46" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="50" s="50">
-      <c r="A50" s="47" t="inlineStr">
+    <row r="47" s="50">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>API-091</t>
         </is>
       </c>
-      <c r="B50" s="41" t="inlineStr">
+      <c r="B47" s="41" t="inlineStr">
         <is>
           <t>마이</t>
         </is>
       </c>
-      <c r="C50" s="42" t="inlineStr">
+      <c r="C47" s="42" t="inlineStr">
         <is>
           <t>/api/me/profile</t>
         </is>
       </c>
-      <c r="D50" s="43" t="inlineStr">
+      <c r="D47" s="43" t="inlineStr">
         <is>
           <t>프로필 수정</t>
         </is>
       </c>
-      <c r="E50" s="44" t="inlineStr">
+      <c r="E47" s="44" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F50" s="44" t="inlineStr">
+      <c r="F47" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G50" s="44" t="inlineStr">
+      <c r="G47" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H50" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I50" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J50" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K50" s="45" t="inlineStr">
+      <c r="H47" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I47" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J47" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L50" s="45" t="inlineStr">
+      <c r="L47" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M50" s="45" t="inlineStr">
+      <c r="M47" s="45" t="inlineStr">
         <is>
           <t>{
   "name","phone","notifications":{}
 }</t>
         </is>
       </c>
-      <c r="N50" s="45" t="inlineStr">
+      <c r="N47" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7102,101 +6804,101 @@
 }</t>
         </is>
       </c>
-      <c r="O50" s="45" t="inlineStr">
+      <c r="O47" s="45" t="inlineStr">
         <is>
           <t>본인인증 상태 유지</t>
         </is>
       </c>
-      <c r="P50" s="46" t="inlineStr">
+      <c r="P47" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q50" s="47" t="inlineStr"/>
-      <c r="R50" s="47" t="inlineStr">
+      <c r="Q47" s="47" t="inlineStr"/>
+      <c r="R47" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005</t>
         </is>
       </c>
-      <c r="S50" s="47" t="inlineStr">
+      <c r="S47" s="47" t="inlineStr">
         <is>
           <t>ZB-U-MY-04</t>
         </is>
       </c>
-      <c r="T50" s="47" t="inlineStr"/>
-      <c r="U50" s="48" t="n">
+      <c r="T47" s="47" t="inlineStr"/>
+      <c r="U47" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="51" s="50">
-      <c r="A51" s="47" t="inlineStr">
+    <row r="48" s="50">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>API-092</t>
         </is>
       </c>
-      <c r="B51" s="41" t="inlineStr">
+      <c r="B48" s="41" t="inlineStr">
         <is>
           <t>마이</t>
         </is>
       </c>
-      <c r="C51" s="42" t="inlineStr">
+      <c r="C48" s="42" t="inlineStr">
         <is>
           <t>/api/me/subscriptions</t>
         </is>
       </c>
-      <c r="D51" s="43" t="inlineStr">
+      <c r="D48" s="43" t="inlineStr">
         <is>
           <t>내 관심/구독/신청함 공고</t>
         </is>
       </c>
-      <c r="E51" s="44" t="inlineStr">
+      <c r="E48" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F51" s="44" t="inlineStr">
+      <c r="F48" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G51" s="44" t="inlineStr">
+      <c r="G48" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H51" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I51" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J51" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K51" s="45" t="inlineStr">
+      <c r="H48" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I48" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J48" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L51" s="45" t="inlineStr">
+      <c r="L48" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M51" s="45" t="inlineStr">
+      <c r="M48" s="45" t="inlineStr">
         <is>
           <t>?type=(string)   // 관심등록|저장됨|신청함</t>
         </is>
       </c>
-      <c r="N51" s="45" t="inlineStr">
+      <c r="N48" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7206,105 +6908,105 @@
 data: { "items":[ {"subscription","status","dday"} ] }</t>
         </is>
       </c>
-      <c r="O51" s="45" t="inlineStr">
+      <c r="O48" s="45" t="inlineStr">
         <is>
           <t>항목에 subscription 요약·statusCode·dday 포함</t>
         </is>
       </c>
-      <c r="P51" s="46" t="inlineStr">
+      <c r="P48" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q51" s="47" t="inlineStr">
+      <c r="Q48" s="47" t="inlineStr">
         <is>
           <t>ITF-005</t>
         </is>
       </c>
-      <c r="R51" s="47" t="inlineStr">
+      <c r="R48" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S51" s="47" t="inlineStr">
+      <c r="S48" s="47" t="inlineStr">
         <is>
           <t>ZB-U-MY-01</t>
         </is>
       </c>
-      <c r="T51" s="47" t="inlineStr"/>
-      <c r="U51" s="48" t="n">
+      <c r="T48" s="47" t="inlineStr"/>
+      <c r="U48" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="52" s="50">
-      <c r="A52" s="47" t="inlineStr">
+    <row r="49" s="50">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>API-093</t>
         </is>
       </c>
-      <c r="B52" s="41" t="inlineStr">
+      <c r="B49" s="41" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C52" s="42" t="inlineStr">
+      <c r="C49" s="42" t="inlineStr">
         <is>
           <t>/api/notifications</t>
         </is>
       </c>
-      <c r="D52" s="43" t="inlineStr">
+      <c r="D49" s="43" t="inlineStr">
         <is>
           <t>알림 목록</t>
         </is>
       </c>
-      <c r="E52" s="44" t="inlineStr">
+      <c r="E49" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F52" s="44" t="inlineStr">
+      <c r="F49" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G52" s="44" t="inlineStr">
+      <c r="G49" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H52" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I52" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J52" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K52" s="45" t="inlineStr">
+      <c r="H49" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I49" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L52" s="45" t="inlineStr">
+      <c r="L49" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M52" s="45" t="inlineStr">
+      <c r="M49" s="45" t="inlineStr">
         <is>
           <t>?page=(int)</t>
         </is>
       </c>
-      <c r="N52" s="45" t="inlineStr">
+      <c r="N49" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7314,99 +7016,99 @@
 data: { "items":[ {"id","type","title","read","createdAt"} ] }</t>
         </is>
       </c>
-      <c r="O52" s="45" t="inlineStr"/>
-      <c r="P52" s="46" t="inlineStr">
+      <c r="O49" s="45" t="inlineStr"/>
+      <c r="P49" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q52" s="47" t="inlineStr"/>
-      <c r="R52" s="47" t="inlineStr">
+      <c r="Q49" s="47" t="inlineStr"/>
+      <c r="R49" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S52" s="47" t="inlineStr">
+      <c r="S49" s="47" t="inlineStr">
         <is>
           <t>ZB-U-COM-05</t>
         </is>
       </c>
-      <c r="T52" s="47" t="inlineStr"/>
-      <c r="U52" s="48" t="n">
+      <c r="T49" s="47" t="inlineStr"/>
+      <c r="U49" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="53" s="50">
-      <c r="A53" s="47" t="inlineStr">
+    <row r="50" s="50">
+      <c r="A50" s="47" t="inlineStr">
         <is>
           <t>API-094</t>
         </is>
       </c>
-      <c r="B53" s="41" t="inlineStr">
+      <c r="B50" s="41" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C53" s="42" t="inlineStr">
+      <c r="C50" s="42" t="inlineStr">
         <is>
           <t>/api/subscriptions-feed/subscribe</t>
         </is>
       </c>
-      <c r="D53" s="43" t="inlineStr">
+      <c r="D50" s="43" t="inlineStr">
         <is>
           <t>공고 구독 설정</t>
         </is>
       </c>
-      <c r="E53" s="44" t="inlineStr">
+      <c r="E50" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F53" s="44" t="inlineStr">
+      <c r="F50" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G53" s="44" t="inlineStr">
+      <c r="G50" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H53" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I53" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J53" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K53" s="45" t="inlineStr">
+      <c r="H50" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I50" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J50" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L53" s="45" t="inlineStr">
+      <c r="L50" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M53" s="45" t="inlineStr">
+      <c r="M50" s="45" t="inlineStr">
         <is>
           <t>{
   "conditions*": {"region","agency","size"}
 }</t>
         </is>
       </c>
-      <c r="N53" s="45" t="inlineStr">
+      <c r="N50" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7415,104 +7117,104 @@
 }</t>
         </is>
       </c>
-      <c r="O53" s="45" t="inlineStr">
+      <c r="O50" s="45" t="inlineStr">
         <is>
           <t>마감임박 알림</t>
         </is>
       </c>
-      <c r="P53" s="46" t="inlineStr">
+      <c r="P50" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q53" s="47" t="inlineStr">
+      <c r="Q50" s="47" t="inlineStr">
         <is>
           <t>ITF-001,ITF-003,ITF-004</t>
         </is>
       </c>
-      <c r="R53" s="47" t="inlineStr">
+      <c r="R50" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S53" s="47" t="inlineStr">
+      <c r="S50" s="47" t="inlineStr">
         <is>
           <t>ZB-U-SUBS-01</t>
         </is>
       </c>
-      <c r="T53" s="47" t="inlineStr"/>
-      <c r="U53" s="48" t="n">
+      <c r="T50" s="47" t="inlineStr"/>
+      <c r="U50" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="54" s="50">
-      <c r="A54" s="47" t="inlineStr">
+    <row r="51" s="50">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>API-095</t>
         </is>
       </c>
-      <c r="B54" s="41" t="inlineStr">
+      <c r="B51" s="41" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C54" s="42" t="inlineStr">
+      <c r="C51" s="42" t="inlineStr">
         <is>
           <t>/api/search</t>
         </is>
       </c>
-      <c r="D54" s="43" t="inlineStr">
+      <c r="D51" s="43" t="inlineStr">
         <is>
           <t>통합 검색(주택·가구)</t>
         </is>
       </c>
-      <c r="E54" s="44" t="inlineStr">
+      <c r="E51" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F54" s="44" t="inlineStr">
+      <c r="F51" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G54" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H54" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I54" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J54" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K54" s="45" t="inlineStr">
+      <c r="G51" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H51" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I51" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json</t>
         </is>
       </c>
-      <c r="L54" s="45" t="inlineStr">
+      <c r="L51" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M54" s="45" t="inlineStr">
+      <c r="M51" s="45" t="inlineStr">
         <is>
           <t>?q=(string)&amp;type=(string)</t>
         </is>
       </c>
-      <c r="N54" s="45" t="inlineStr">
+      <c r="N51" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7522,103 +7224,103 @@
 data: { "subscriptions":[], "floorplans":[], "products":[] }</t>
         </is>
       </c>
-      <c r="O54" s="45" t="inlineStr">
+      <c r="O51" s="45" t="inlineStr">
         <is>
           <t>유형별 결과</t>
         </is>
       </c>
-      <c r="P54" s="46" t="inlineStr">
+      <c r="P51" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q54" s="47" t="inlineStr"/>
-      <c r="R54" s="47" t="inlineStr">
+      <c r="Q51" s="47" t="inlineStr"/>
+      <c r="R51" s="47" t="inlineStr">
         <is>
           <t>ERR-005</t>
         </is>
       </c>
-      <c r="S54" s="47" t="inlineStr">
-        <is>
-          <t>ZB-U-MAIN-02</t>
-        </is>
-      </c>
-      <c r="T54" s="47" t="inlineStr"/>
-      <c r="U54" s="48" t="n">
+      <c r="S51" s="47" t="inlineStr">
+        <is>
+          <t>ZB-U-COM-01</t>
+        </is>
+      </c>
+      <c r="T51" s="47" t="inlineStr"/>
+      <c r="U51" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="55" s="50">
-      <c r="A55" s="47" t="inlineStr">
+    <row r="52" s="50">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>API-100</t>
         </is>
       </c>
-      <c r="B55" s="41" t="inlineStr">
+      <c r="B52" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C55" s="42" t="inlineStr">
+      <c r="C52" s="42" t="inlineStr">
         <is>
           <t>/api/admin/auth/login</t>
         </is>
       </c>
-      <c r="D55" s="43" t="inlineStr">
+      <c r="D52" s="43" t="inlineStr">
         <is>
           <t>관리자 로그인</t>
         </is>
       </c>
-      <c r="E55" s="44" t="inlineStr">
+      <c r="E52" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F55" s="44" t="inlineStr">
+      <c r="F52" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G55" s="44" t="inlineStr">
+      <c r="G52" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H55" s="44" t="inlineStr">
+      <c r="H52" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I55" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J55" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K55" s="45" t="inlineStr">
+      <c r="I52" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L55" s="45" t="inlineStr">
+      <c r="L52" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M55" s="45" t="inlineStr">
+      <c r="M52" s="45" t="inlineStr">
         <is>
           <t>{
   "email*","password*","otp"
 }</t>
         </is>
       </c>
-      <c r="N55" s="45" t="inlineStr">
+      <c r="N52" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7628,109 +7330,109 @@
 data: { "accessToken","admin" }</t>
         </is>
       </c>
-      <c r="O55" s="45" t="inlineStr">
+      <c r="O52" s="45" t="inlineStr">
         <is>
           <t>2차 인증</t>
         </is>
       </c>
-      <c r="P55" s="46" t="inlineStr">
+      <c r="P52" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q55" s="47" t="inlineStr">
+      <c r="Q52" s="47" t="inlineStr">
         <is>
           <t>ITF-012</t>
         </is>
       </c>
-      <c r="R55" s="47" t="inlineStr">
+      <c r="R52" s="47" t="inlineStr">
         <is>
           <t>ERR-002,ERR-003</t>
         </is>
       </c>
-      <c r="S55" s="47" t="inlineStr">
+      <c r="S52" s="47" t="inlineStr">
         <is>
           <t>ZB-A-AUTH-01</t>
         </is>
       </c>
-      <c r="T55" s="47" t="inlineStr">
+      <c r="T52" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U55" s="48" t="n">
+      <c r="U52" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="56" s="50">
-      <c r="A56" s="47" t="inlineStr">
+    <row r="53" s="50">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>API-101</t>
         </is>
       </c>
-      <c r="B56" s="41" t="inlineStr">
+      <c r="B53" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C56" s="42" t="inlineStr">
+      <c r="C53" s="42" t="inlineStr">
         <is>
           <t>/api/admin/dashboard</t>
         </is>
       </c>
-      <c r="D56" s="43" t="inlineStr">
+      <c r="D53" s="43" t="inlineStr">
         <is>
           <t>운영 대시보드 지표</t>
         </is>
       </c>
-      <c r="E56" s="44" t="inlineStr">
+      <c r="E53" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F56" s="44" t="inlineStr">
+      <c r="F53" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G56" s="44" t="inlineStr">
+      <c r="G53" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H56" s="44" t="inlineStr">
+      <c r="H53" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I56" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J56" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K56" s="45" t="inlineStr">
+      <c r="I53" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J53" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L56" s="45" t="inlineStr">
+      <c r="L53" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M56" s="45" t="inlineStr">
+      <c r="M53" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N56" s="45" t="inlineStr">
+      <c r="N53" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7740,101 +7442,101 @@
 data: { "subscriptions","members","orders","traffic" }</t>
         </is>
       </c>
-      <c r="O56" s="45" t="inlineStr"/>
-      <c r="P56" s="46" t="inlineStr">
+      <c r="O53" s="45" t="inlineStr"/>
+      <c r="P53" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q56" s="47" t="inlineStr"/>
-      <c r="R56" s="47" t="inlineStr">
+      <c r="Q53" s="47" t="inlineStr"/>
+      <c r="R53" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S56" s="47" t="inlineStr">
+      <c r="S53" s="47" t="inlineStr">
         <is>
           <t>ZB-A-DASH-01</t>
         </is>
       </c>
-      <c r="T56" s="47" t="inlineStr">
+      <c r="T53" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U56" s="48" t="n">
+      <c r="U53" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="57" s="50">
-      <c r="A57" s="47" t="inlineStr">
+    <row r="54" s="50">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>API-110</t>
         </is>
       </c>
-      <c r="B57" s="41" t="inlineStr">
+      <c r="B54" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C57" s="42" t="inlineStr">
+      <c r="C54" s="42" t="inlineStr">
         <is>
           <t>/api/admin/subscriptions</t>
         </is>
       </c>
-      <c r="D57" s="43" t="inlineStr">
+      <c r="D54" s="43" t="inlineStr">
         <is>
           <t>공고 목록 관리</t>
         </is>
       </c>
-      <c r="E57" s="44" t="inlineStr">
+      <c r="E54" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F57" s="44" t="inlineStr">
+      <c r="F54" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G57" s="44" t="inlineStr">
+      <c r="G54" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H57" s="44" t="inlineStr">
+      <c r="H54" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I57" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J57" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K57" s="45" t="inlineStr">
+      <c r="I54" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J54" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L57" s="45" t="inlineStr">
+      <c r="L54" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M57" s="45" t="inlineStr">
+      <c r="M54" s="45" t="inlineStr">
         <is>
           <t>?status=(string)&amp;page=(int)</t>
         </is>
       </c>
-      <c r="N57" s="45" t="inlineStr">
+      <c r="N54" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7844,107 +7546,107 @@
 data: { "items":[], "page","totalCount" }</t>
         </is>
       </c>
-      <c r="O57" s="45" t="inlineStr"/>
-      <c r="P57" s="46" t="inlineStr">
+      <c r="O54" s="45" t="inlineStr"/>
+      <c r="P54" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q57" s="47" t="inlineStr">
+      <c r="Q54" s="47" t="inlineStr">
         <is>
           <t>ITF-001</t>
         </is>
       </c>
-      <c r="R57" s="47" t="inlineStr">
+      <c r="R54" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S57" s="47" t="inlineStr">
+      <c r="S54" s="47" t="inlineStr">
         <is>
           <t>ZB-A-SUBS-01</t>
         </is>
       </c>
-      <c r="T57" s="47" t="inlineStr">
+      <c r="T54" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U57" s="48" t="n">
+      <c r="U54" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="58" s="50">
-      <c r="A58" s="47" t="inlineStr">
+    <row r="55" s="50">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>API-111</t>
         </is>
       </c>
-      <c r="B58" s="41" t="inlineStr">
+      <c r="B55" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C58" s="42" t="inlineStr">
+      <c r="C55" s="42" t="inlineStr">
         <is>
           <t>/api/admin/subscriptions</t>
         </is>
       </c>
-      <c r="D58" s="43" t="inlineStr">
+      <c r="D55" s="43" t="inlineStr">
         <is>
           <t>공고 등록</t>
         </is>
       </c>
-      <c r="E58" s="44" t="inlineStr">
+      <c r="E55" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F58" s="44" t="inlineStr">
+      <c r="F55" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G58" s="44" t="inlineStr">
+      <c r="G55" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H58" s="44" t="inlineStr">
+      <c r="H55" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I58" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J58" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K58" s="45" t="inlineStr">
+      <c r="I55" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L58" s="45" t="inlineStr">
+      <c r="L55" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M58" s="45" t="inlineStr">
+      <c r="M55" s="45" t="inlineStr">
         <is>
           <t>{
   "title*","agencyCode*","schedule*","units*":[]
 }</t>
         </is>
       </c>
-      <c r="N58" s="45" t="inlineStr">
+      <c r="N55" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -7954,107 +7656,107 @@
 data: { "id" }</t>
         </is>
       </c>
-      <c r="O58" s="45" t="inlineStr"/>
-      <c r="P58" s="46" t="inlineStr">
+      <c r="O55" s="45" t="inlineStr"/>
+      <c r="P55" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q58" s="47" t="inlineStr">
+      <c r="Q55" s="47" t="inlineStr">
         <is>
           <t>ITF-001</t>
         </is>
       </c>
-      <c r="R58" s="47" t="inlineStr">
+      <c r="R55" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005</t>
         </is>
       </c>
-      <c r="S58" s="47" t="inlineStr">
+      <c r="S55" s="47" t="inlineStr">
         <is>
           <t>ZB-A-SUBS-02</t>
         </is>
       </c>
-      <c r="T58" s="47" t="inlineStr">
+      <c r="T55" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U58" s="48" t="n">
+      <c r="U55" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="59" s="50">
-      <c r="A59" s="47" t="inlineStr">
+    <row r="56" s="50">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>API-112</t>
         </is>
       </c>
-      <c r="B59" s="41" t="inlineStr">
+      <c r="B56" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C59" s="42" t="inlineStr">
+      <c r="C56" s="42" t="inlineStr">
         <is>
           <t>/api/admin/subscriptions/{id}</t>
         </is>
       </c>
-      <c r="D59" s="43" t="inlineStr">
+      <c r="D56" s="43" t="inlineStr">
         <is>
           <t>공고 수정</t>
         </is>
       </c>
-      <c r="E59" s="44" t="inlineStr">
+      <c r="E56" s="44" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F59" s="44" t="inlineStr">
+      <c r="F56" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G59" s="44" t="inlineStr">
+      <c r="G56" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H59" s="44" t="inlineStr">
+      <c r="H56" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I59" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J59" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K59" s="45" t="inlineStr">
+      <c r="I56" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J56" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L59" s="45" t="inlineStr">
+      <c r="L56" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M59" s="45" t="inlineStr">
+      <c r="M56" s="45" t="inlineStr">
         <is>
           <t>{
   "title","schedule","units":[]
 }</t>
         </is>
       </c>
-      <c r="N59" s="45" t="inlineStr">
+      <c r="N56" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -8063,101 +7765,101 @@
 }</t>
         </is>
       </c>
-      <c r="O59" s="45" t="inlineStr"/>
-      <c r="P59" s="46" t="inlineStr">
+      <c r="O56" s="45" t="inlineStr"/>
+      <c r="P56" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q59" s="47" t="inlineStr"/>
-      <c r="R59" s="47" t="inlineStr">
+      <c r="Q56" s="47" t="inlineStr"/>
+      <c r="R56" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S59" s="47" t="inlineStr">
+      <c r="S56" s="47" t="inlineStr">
         <is>
           <t>ZB-A-SUBS-02</t>
         </is>
       </c>
-      <c r="T59" s="47" t="inlineStr">
+      <c r="T56" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U59" s="48" t="n">
+      <c r="U56" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="60" s="50">
-      <c r="A60" s="47" t="inlineStr">
+    <row r="57" s="50">
+      <c r="A57" s="47" t="inlineStr">
         <is>
           <t>API-113</t>
         </is>
       </c>
-      <c r="B60" s="41" t="inlineStr">
+      <c r="B57" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C60" s="42" t="inlineStr">
+      <c r="C57" s="42" t="inlineStr">
         <is>
           <t>/api/admin/subscriptions/{id}</t>
         </is>
       </c>
-      <c r="D60" s="43" t="inlineStr">
+      <c r="D57" s="43" t="inlineStr">
         <is>
           <t>공고 삭제</t>
         </is>
       </c>
-      <c r="E60" s="44" t="inlineStr">
+      <c r="E57" s="44" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="F60" s="44" t="inlineStr">
+      <c r="F57" s="44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G60" s="44" t="inlineStr">
+      <c r="G57" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H60" s="44" t="inlineStr">
+      <c r="H57" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I60" s="44" t="inlineStr">
+      <c r="I57" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="J60" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K60" s="45" t="inlineStr">
+      <c r="J57" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L60" s="45" t="inlineStr">
+      <c r="L57" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M60" s="45" t="inlineStr">
+      <c r="M57" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N60" s="45" t="inlineStr">
+      <c r="N57" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -8166,107 +7868,107 @@
 }</t>
         </is>
       </c>
-      <c r="O60" s="45" t="inlineStr">
+      <c r="O57" s="45" t="inlineStr">
         <is>
           <t>관리자만</t>
         </is>
       </c>
-      <c r="P60" s="46" t="inlineStr">
+      <c r="P57" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q60" s="47" t="inlineStr"/>
-      <c r="R60" s="47" t="inlineStr">
+      <c r="Q57" s="47" t="inlineStr"/>
+      <c r="R57" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S60" s="47" t="inlineStr">
+      <c r="S57" s="47" t="inlineStr">
         <is>
           <t>ZB-A-SUBS-01</t>
         </is>
       </c>
-      <c r="T60" s="47" t="inlineStr">
+      <c r="T57" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U60" s="48" t="n">
+      <c r="U57" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="61" s="50">
-      <c r="A61" s="47" t="inlineStr">
+    <row r="58" s="50">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>API-114</t>
         </is>
       </c>
-      <c r="B61" s="41" t="inlineStr">
+      <c r="B58" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C61" s="42" t="inlineStr">
+      <c r="C58" s="42" t="inlineStr">
         <is>
           <t>/api/admin/subscriptions/sync</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
+      <c r="D58" s="43" t="inlineStr">
         <is>
           <t>공공데이터 동기화</t>
         </is>
       </c>
-      <c r="E61" s="44" t="inlineStr">
+      <c r="E58" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F61" s="44" t="inlineStr">
+      <c r="F58" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G61" s="44" t="inlineStr">
+      <c r="G58" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H61" s="44" t="inlineStr">
+      <c r="H58" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I61" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J61" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K61" s="45" t="inlineStr">
+      <c r="I58" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J58" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L61" s="45" t="inlineStr">
+      <c r="L58" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M61" s="45" t="inlineStr">
+      <c r="M58" s="45" t="inlineStr">
         <is>
           <t>{
   "agencyCode*": (int)
 }</t>
         </is>
       </c>
-      <c r="N61" s="45" t="inlineStr">
+      <c r="N58" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -8276,109 +7978,109 @@
 data: { "jobId","synced":(int) }</t>
         </is>
       </c>
-      <c r="O61" s="45" t="inlineStr">
+      <c r="O58" s="45" t="inlineStr">
         <is>
           <t>LH/SH/GH/IH 수집 — applyUrl(신청링크)·address·lat·lng 정규화 매핑 포함</t>
         </is>
       </c>
-      <c r="P61" s="46" t="inlineStr">
+      <c r="P58" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q61" s="47" t="inlineStr">
+      <c r="Q58" s="47" t="inlineStr">
         <is>
           <t>ITF-001</t>
         </is>
       </c>
-      <c r="R61" s="47" t="inlineStr">
+      <c r="R58" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-010</t>
         </is>
       </c>
-      <c r="S61" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SUBS-03</t>
-        </is>
-      </c>
-      <c r="T61" s="47" t="inlineStr">
+      <c r="S58" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SUBS-01</t>
+        </is>
+      </c>
+      <c r="T58" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U61" s="48" t="n">
+      <c r="U58" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="62" s="50">
-      <c r="A62" s="47" t="inlineStr">
+    <row r="59" s="50">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>API-120</t>
         </is>
       </c>
-      <c r="B62" s="41" t="inlineStr">
+      <c r="B59" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C62" s="42" t="inlineStr">
+      <c r="C59" s="42" t="inlineStr">
         <is>
           <t>/api/admin/floorplans</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr">
+      <c r="D59" s="43" t="inlineStr">
         <is>
           <t>공고 연계 평면도/자산 목록</t>
         </is>
       </c>
-      <c r="E62" s="44" t="inlineStr">
+      <c r="E59" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F62" s="44" t="inlineStr">
+      <c r="F59" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G62" s="44" t="inlineStr">
+      <c r="G59" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H62" s="44" t="inlineStr">
+      <c r="H59" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I62" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J62" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K62" s="45" t="inlineStr">
+      <c r="I59" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J59" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L62" s="45" t="inlineStr">
+      <c r="L59" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M62" s="45" t="inlineStr">
+      <c r="M59" s="45" t="inlineStr">
         <is>
           <t>?page=(int)</t>
         </is>
       </c>
-      <c r="N62" s="45" t="inlineStr">
+      <c r="N59" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -8388,103 +8090,103 @@
 data: { "items":[] }</t>
         </is>
       </c>
-      <c r="O62" s="45" t="inlineStr"/>
-      <c r="P62" s="46" t="inlineStr">
+      <c r="O59" s="45" t="inlineStr"/>
+      <c r="P59" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q62" s="47" t="inlineStr"/>
-      <c r="R62" s="47" t="inlineStr">
+      <c r="Q59" s="47" t="inlineStr"/>
+      <c r="R59" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S62" s="47" t="inlineStr">
+      <c r="S59" s="47" t="inlineStr">
         <is>
           <t>ZB-A-PLAN-01</t>
         </is>
       </c>
-      <c r="T62" s="47" t="inlineStr">
+      <c r="T59" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U62" s="48" t="n">
+      <c r="U59" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="63" s="50">
-      <c r="A63" s="47" t="inlineStr">
+    <row r="60" s="50">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>API-121</t>
         </is>
       </c>
-      <c r="B63" s="41" t="inlineStr">
+      <c r="B60" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C63" s="42" t="inlineStr">
+      <c r="C60" s="42" t="inlineStr">
         <is>
           <t>/api/admin/floorplans</t>
         </is>
       </c>
-      <c r="D63" s="43" t="inlineStr">
+      <c r="D60" s="43" t="inlineStr">
         <is>
           <t>공고 연계 평면도 등록</t>
         </is>
       </c>
-      <c r="E63" s="44" t="inlineStr">
+      <c r="E60" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F63" s="44" t="inlineStr">
+      <c r="F60" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G63" s="44" t="inlineStr">
+      <c r="G60" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H63" s="44" t="inlineStr">
+      <c r="H60" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I63" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J63" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K63" s="45" t="inlineStr">
+      <c r="I60" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J60" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L63" s="45" t="inlineStr">
+      <c r="L60" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M63" s="45" t="inlineStr">
+      <c r="M60" s="45" t="inlineStr">
         <is>
           <t>{
   "size*","type*","dimensions*","subscriptionId"
 }</t>
         </is>
       </c>
-      <c r="N63" s="45" t="inlineStr">
+      <c r="N60" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -8493,103 +8195,103 @@
 }</t>
         </is>
       </c>
-      <c r="O63" s="45" t="inlineStr"/>
-      <c r="P63" s="46" t="inlineStr">
+      <c r="O60" s="45" t="inlineStr"/>
+      <c r="P60" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q63" s="47" t="inlineStr"/>
-      <c r="R63" s="47" t="inlineStr">
+      <c r="Q60" s="47" t="inlineStr"/>
+      <c r="R60" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005</t>
         </is>
       </c>
-      <c r="S63" s="47" t="inlineStr">
+      <c r="S60" s="47" t="inlineStr">
         <is>
           <t>ZB-A-PLAN-02</t>
         </is>
       </c>
-      <c r="T63" s="47" t="inlineStr">
+      <c r="T60" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U63" s="48" t="n">
+      <c r="U60" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="64" s="50">
-      <c r="A64" s="47" t="inlineStr">
+    <row r="61" s="50">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>API-122</t>
         </is>
       </c>
-      <c r="B64" s="41" t="inlineStr">
+      <c r="B61" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C64" s="42" t="inlineStr">
+      <c r="C61" s="42" t="inlineStr">
         <is>
           <t>/api/admin/floorplans/{id}/assets</t>
         </is>
       </c>
-      <c r="D64" s="43" t="inlineStr">
+      <c r="D61" s="43" t="inlineStr">
         <is>
           <t>2D/3D(WebGL) 자산 업로드</t>
         </is>
       </c>
-      <c r="E64" s="44" t="inlineStr">
+      <c r="E61" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F64" s="44" t="inlineStr">
+      <c r="F61" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G64" s="44" t="inlineStr">
+      <c r="G61" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H64" s="44" t="inlineStr">
+      <c r="H61" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I64" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J64" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K64" s="45" t="inlineStr">
+      <c r="I61" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L64" s="45" t="inlineStr">
+      <c r="L61" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M64" s="45" t="inlineStr">
+      <c r="M61" s="45" t="inlineStr">
         <is>
           <t>(multipart/form-data)
 • file*: (binary)
 • type*: 2d|3d</t>
         </is>
       </c>
-      <c r="N64" s="45" t="inlineStr">
+      <c r="N61" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -8599,107 +8301,107 @@
 data: { "assetUrl" }</t>
         </is>
       </c>
-      <c r="O64" s="45" t="inlineStr">
+      <c r="O61" s="45" t="inlineStr">
         <is>
           <t>모델/씬 업로드</t>
         </is>
       </c>
-      <c r="P64" s="46" t="inlineStr">
+      <c r="P61" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q64" s="47" t="inlineStr"/>
-      <c r="R64" s="47" t="inlineStr">
+      <c r="Q61" s="47" t="inlineStr"/>
+      <c r="R61" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005,ERR-015</t>
         </is>
       </c>
-      <c r="S64" s="47" t="inlineStr">
+      <c r="S61" s="47" t="inlineStr">
         <is>
           <t>ZB-A-PLAN-02</t>
         </is>
       </c>
-      <c r="T64" s="47" t="inlineStr">
+      <c r="T61" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U64" s="48" t="n">
+      <c r="U61" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="65" s="50">
-      <c r="A65" s="47" t="inlineStr">
+    <row r="62" s="50">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>API-130</t>
         </is>
       </c>
-      <c r="B65" s="41" t="inlineStr">
+      <c r="B62" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C65" s="42" t="inlineStr">
+      <c r="C62" s="42" t="inlineStr">
         <is>
           <t>/api/admin/inspirations</t>
         </is>
       </c>
-      <c r="D65" s="43" t="inlineStr">
-        <is>
-          <t>인테리어 영감 관리</t>
-        </is>
-      </c>
-      <c r="E65" s="44" t="inlineStr">
+      <c r="D62" s="43" t="inlineStr">
+        <is>
+          <t>집구경(인테리어 영감) 관리</t>
+        </is>
+      </c>
+      <c r="E62" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F65" s="44" t="inlineStr">
+      <c r="F62" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G65" s="44" t="inlineStr">
+      <c r="G62" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H65" s="44" t="inlineStr">
+      <c r="H62" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I65" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J65" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K65" s="45" t="inlineStr">
+      <c r="I62" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L65" s="45" t="inlineStr">
+      <c r="L62" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M65" s="45" t="inlineStr">
+      <c r="M62" s="45" t="inlineStr">
         <is>
           <t>{
   "space*","image*","taggedProducts":[]
 }</t>
         </is>
       </c>
-      <c r="N65" s="45" t="inlineStr">
+      <c r="N62" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -8708,111 +8410,111 @@
 }</t>
         </is>
       </c>
-      <c r="O65" s="45" t="inlineStr">
+      <c r="O62" s="45" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="P65" s="46" t="inlineStr">
+      <c r="P62" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q65" s="47" t="inlineStr">
+      <c r="Q62" s="47" t="inlineStr">
         <is>
           <t>ITF-009</t>
         </is>
       </c>
-      <c r="R65" s="47" t="inlineStr">
+      <c r="R62" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S65" s="47" t="inlineStr">
+      <c r="S62" s="47" t="inlineStr">
         <is>
           <t>ZB-A-TOUR-01</t>
         </is>
       </c>
-      <c r="T65" s="47" t="inlineStr">
+      <c r="T62" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U65" s="48" t="n">
+      <c r="U62" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="66" s="50">
-      <c r="A66" s="47" t="inlineStr">
-        <is>
-          <t>API-140</t>
-        </is>
-      </c>
-      <c r="B66" s="41" t="inlineStr">
+    <row r="63" s="50">
+      <c r="A63" s="47" t="inlineStr">
+        <is>
+          <t>API-150</t>
+        </is>
+      </c>
+      <c r="B63" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C66" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/showrooms</t>
-        </is>
-      </c>
-      <c r="D66" s="43" t="inlineStr">
-        <is>
-          <t>쇼룸/파트너 관리</t>
-        </is>
-      </c>
-      <c r="E66" s="44" t="inlineStr">
+      <c r="C63" s="42" t="inlineStr">
+        <is>
+          <t>/api/admin/products</t>
+        </is>
+      </c>
+      <c r="D63" s="43" t="inlineStr">
+        <is>
+          <t>상품 관리(2차)</t>
+        </is>
+      </c>
+      <c r="E63" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F66" s="44" t="inlineStr">
+      <c r="F63" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G66" s="44" t="inlineStr">
+      <c r="G63" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H66" s="44" t="inlineStr">
+      <c r="H63" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I66" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J66" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K66" s="45" t="inlineStr">
+      <c r="I63" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L66" s="45" t="inlineStr">
+      <c r="L63" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M66" s="45" t="inlineStr">
+      <c r="M63" s="45" t="inlineStr">
         <is>
           <t>{
-  "name*","address*","lat*","lng*","slots":[]
+  "brand*","name*","price*","category*","stock*"
 }</t>
         </is>
       </c>
-      <c r="N66" s="45" t="inlineStr">
+      <c r="N63" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -8821,218 +8523,109 @@
 }</t>
         </is>
       </c>
-      <c r="O66" s="45" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-      <c r="P66" s="46" t="inlineStr">
+      <c r="O63" s="45" t="inlineStr">
+        <is>
+          <t>CRUD·2차</t>
+        </is>
+      </c>
+      <c r="P63" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q66" s="47" t="inlineStr"/>
-      <c r="R66" s="47" t="inlineStr">
-        <is>
-          <t>ERR-003</t>
-        </is>
-      </c>
-      <c r="S66" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOW-01</t>
-        </is>
-      </c>
-      <c r="T66" s="47" t="inlineStr">
-        <is>
-          <t>도출</t>
-        </is>
-      </c>
-      <c r="U66" s="48" t="n">
+      <c r="Q63" s="47" t="inlineStr">
+        <is>
+          <t>ITF-007</t>
+        </is>
+      </c>
+      <c r="R63" s="47" t="inlineStr">
+        <is>
+          <t>ERR-003,ERR-005</t>
+        </is>
+      </c>
+      <c r="S63" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SHOP-01</t>
+        </is>
+      </c>
+      <c r="T63" s="47" t="inlineStr">
+        <is>
+          <t>도출·2차</t>
+        </is>
+      </c>
+      <c r="U63" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="67" s="50">
-      <c r="A67" s="47" t="inlineStr">
-        <is>
-          <t>API-150</t>
-        </is>
-      </c>
-      <c r="B67" s="41" t="inlineStr">
+    <row r="64" s="50">
+      <c r="A64" s="47" t="inlineStr">
+        <is>
+          <t>API-160</t>
+        </is>
+      </c>
+      <c r="B64" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C67" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/products</t>
-        </is>
-      </c>
-      <c r="D67" s="43" t="inlineStr">
-        <is>
-          <t>상품 관리(2차)</t>
-        </is>
-      </c>
-      <c r="E67" s="44" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F67" s="44" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G67" s="44" t="inlineStr">
+      <c r="C64" s="42" t="inlineStr">
+        <is>
+          <t>/api/admin/orders</t>
+        </is>
+      </c>
+      <c r="D64" s="43" t="inlineStr">
+        <is>
+          <t>주문/배송 관리(2차)</t>
+        </is>
+      </c>
+      <c r="E64" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F64" s="44" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G64" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H67" s="44" t="inlineStr">
+      <c r="H64" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I67" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J67" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K67" s="45" t="inlineStr">
+      <c r="I64" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J64" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L67" s="45" t="inlineStr">
+      <c r="L64" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M67" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "brand*","name*","price*","category*","stock*"
-}</t>
-        </is>
-      </c>
-      <c r="N67" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "success": (boolean),
-  "data": (object|null),
-  "error": (object|null)
-}</t>
-        </is>
-      </c>
-      <c r="O67" s="45" t="inlineStr">
-        <is>
-          <t>CRUD·2차</t>
-        </is>
-      </c>
-      <c r="P67" s="46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q67" s="47" t="inlineStr">
-        <is>
-          <t>ITF-007</t>
-        </is>
-      </c>
-      <c r="R67" s="47" t="inlineStr">
-        <is>
-          <t>ERR-003,ERR-005</t>
-        </is>
-      </c>
-      <c r="S67" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOP-01</t>
-        </is>
-      </c>
-      <c r="T67" s="47" t="inlineStr">
-        <is>
-          <t>도출·2차</t>
-        </is>
-      </c>
-      <c r="U67" s="48" t="n">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="68" s="50">
-      <c r="A68" s="47" t="inlineStr">
-        <is>
-          <t>API-160</t>
-        </is>
-      </c>
-      <c r="B68" s="41" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="C68" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/orders</t>
-        </is>
-      </c>
-      <c r="D68" s="43" t="inlineStr">
-        <is>
-          <t>주문/배송 관리(2차)</t>
-        </is>
-      </c>
-      <c r="E68" s="44" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F68" s="44" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G68" s="44" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H68" s="44" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I68" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J68" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K68" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Authorization: Bearer {accessToken}</t>
-        </is>
-      </c>
-      <c r="L68" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Date: (표준)</t>
-        </is>
-      </c>
-      <c r="M68" s="45" t="inlineStr">
+      <c r="M64" s="45" t="inlineStr">
         <is>
           <t>?status=(string)</t>
         </is>
       </c>
-      <c r="N68" s="45" t="inlineStr">
+      <c r="N64" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -9042,111 +8635,111 @@
 data: { "items":[] }</t>
         </is>
       </c>
-      <c r="O68" s="45" t="inlineStr">
+      <c r="O64" s="45" t="inlineStr">
         <is>
           <t>상태 변경 PUT 별도</t>
         </is>
       </c>
-      <c r="P68" s="46" t="inlineStr">
+      <c r="P64" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q68" s="47" t="inlineStr">
+      <c r="Q64" s="47" t="inlineStr">
         <is>
           <t>ITF-006</t>
         </is>
       </c>
-      <c r="R68" s="47" t="inlineStr">
+      <c r="R64" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S68" s="47" t="inlineStr">
+      <c r="S64" s="47" t="inlineStr">
         <is>
           <t>ZB-A-ORDER-01</t>
         </is>
       </c>
-      <c r="T68" s="47" t="inlineStr">
+      <c r="T64" s="47" t="inlineStr">
         <is>
           <t>도출·2차</t>
         </is>
       </c>
-      <c r="U68" s="48" t="n">
+      <c r="U64" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="69" s="50">
-      <c r="A69" s="47" t="inlineStr">
+    <row r="65" s="50">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>API-161</t>
         </is>
       </c>
-      <c r="B69" s="41" t="inlineStr">
+      <c r="B65" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C69" s="42" t="inlineStr">
+      <c r="C65" s="42" t="inlineStr">
         <is>
           <t>/api/admin/orders/{id}</t>
         </is>
       </c>
-      <c r="D69" s="43" t="inlineStr">
+      <c r="D65" s="43" t="inlineStr">
         <is>
           <t>배송 상태 변경(2차)</t>
         </is>
       </c>
-      <c r="E69" s="44" t="inlineStr">
+      <c r="E65" s="44" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F69" s="44" t="inlineStr">
+      <c r="F65" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G69" s="44" t="inlineStr">
+      <c r="G65" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H69" s="44" t="inlineStr">
+      <c r="H65" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I69" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J69" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K69" s="45" t="inlineStr">
+      <c r="I65" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L69" s="45" t="inlineStr">
+      <c r="L65" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M69" s="45" t="inlineStr">
+      <c r="M65" s="45" t="inlineStr">
         <is>
           <t>{
   "shippingStatus*": (string)
 }</t>
         </is>
       </c>
-      <c r="N69" s="45" t="inlineStr">
+      <c r="N65" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -9155,109 +8748,109 @@
 }</t>
         </is>
       </c>
-      <c r="O69" s="45" t="inlineStr">
+      <c r="O65" s="45" t="inlineStr">
         <is>
           <t>준비중/배송중/배송완료</t>
         </is>
       </c>
-      <c r="P69" s="46" t="inlineStr">
+      <c r="P65" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q69" s="47" t="inlineStr">
+      <c r="Q65" s="47" t="inlineStr">
         <is>
           <t>ITF-006</t>
         </is>
       </c>
-      <c r="R69" s="47" t="inlineStr">
+      <c r="R65" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S69" s="47" t="inlineStr">
+      <c r="S65" s="47" t="inlineStr">
         <is>
           <t>ZB-A-ORDER-01</t>
         </is>
       </c>
-      <c r="T69" s="47" t="inlineStr">
+      <c r="T65" s="47" t="inlineStr">
         <is>
           <t>도출·2차</t>
         </is>
       </c>
-      <c r="U69" s="48" t="n">
+      <c r="U65" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="70" s="50">
-      <c r="A70" s="47" t="inlineStr">
+    <row r="66" s="50">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>API-170</t>
         </is>
       </c>
-      <c r="B70" s="41" t="inlineStr">
+      <c r="B66" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C70" s="42" t="inlineStr">
+      <c r="C66" s="42" t="inlineStr">
         <is>
           <t>/api/admin/members</t>
         </is>
       </c>
-      <c r="D70" s="43" t="inlineStr">
+      <c r="D66" s="43" t="inlineStr">
         <is>
           <t>회원 관리</t>
         </is>
       </c>
-      <c r="E70" s="44" t="inlineStr">
+      <c r="E66" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F70" s="44" t="inlineStr">
+      <c r="F66" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G70" s="44" t="inlineStr">
+      <c r="G66" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H70" s="44" t="inlineStr">
+      <c r="H66" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I70" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J70" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K70" s="45" t="inlineStr">
+      <c r="I66" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L70" s="45" t="inlineStr">
+      <c r="L66" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M70" s="45" t="inlineStr">
+      <c r="M66" s="45" t="inlineStr">
         <is>
           <t>?keyword=(string)&amp;status=(string)</t>
         </is>
       </c>
-      <c r="N70" s="45" t="inlineStr">
+      <c r="N66" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -9267,111 +8860,111 @@
 data: { "items":[] }</t>
         </is>
       </c>
-      <c r="O70" s="45" t="inlineStr">
+      <c r="O66" s="45" t="inlineStr">
         <is>
           <t>상태 변경 PUT 별도</t>
         </is>
       </c>
-      <c r="P70" s="46" t="inlineStr">
+      <c r="P66" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q70" s="47" t="inlineStr">
+      <c r="Q66" s="47" t="inlineStr">
         <is>
           <t>ITF-012</t>
         </is>
       </c>
-      <c r="R70" s="47" t="inlineStr">
+      <c r="R66" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S70" s="47" t="inlineStr">
+      <c r="S66" s="47" t="inlineStr">
         <is>
           <t>ZB-A-MEMBER-01</t>
         </is>
       </c>
-      <c r="T70" s="47" t="inlineStr">
+      <c r="T66" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U70" s="48" t="n">
+      <c r="U66" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="71" s="50">
-      <c r="A71" s="47" t="inlineStr">
+    <row r="67" s="50">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>API-171</t>
         </is>
       </c>
-      <c r="B71" s="41" t="inlineStr">
+      <c r="B67" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C71" s="42" t="inlineStr">
+      <c r="C67" s="42" t="inlineStr">
         <is>
           <t>/api/admin/members/{id}</t>
         </is>
       </c>
-      <c r="D71" s="43" t="inlineStr">
+      <c r="D67" s="43" t="inlineStr">
         <is>
           <t>회원 상태 변경</t>
         </is>
       </c>
-      <c r="E71" s="44" t="inlineStr">
+      <c r="E67" s="44" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F71" s="44" t="inlineStr">
+      <c r="F67" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G71" s="44" t="inlineStr">
+      <c r="G67" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H71" s="44" t="inlineStr">
+      <c r="H67" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I71" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J71" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K71" s="45" t="inlineStr">
+      <c r="I67" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L71" s="45" t="inlineStr">
+      <c r="L67" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M71" s="45" t="inlineStr">
+      <c r="M67" s="45" t="inlineStr">
         <is>
           <t>{
   "status*": "정상|정지|탈퇴"
 }</t>
         </is>
       </c>
-      <c r="N71" s="45" t="inlineStr">
+      <c r="N67" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -9380,96 +8973,96 @@
 }</t>
         </is>
       </c>
-      <c r="O71" s="45" t="inlineStr"/>
-      <c r="P71" s="46" t="inlineStr">
+      <c r="O67" s="45" t="inlineStr"/>
+      <c r="P67" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q71" s="47" t="inlineStr"/>
-      <c r="R71" s="47" t="inlineStr">
+      <c r="Q67" s="47" t="inlineStr"/>
+      <c r="R67" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S71" s="47" t="inlineStr">
+      <c r="S67" s="47" t="inlineStr">
         <is>
           <t>ZB-A-MEMBER-01</t>
         </is>
       </c>
-      <c r="T71" s="47" t="inlineStr">
+      <c r="T67" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U71" s="48" t="n">
+      <c r="U67" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="72" s="50">
-      <c r="A72" s="47" t="inlineStr">
+    <row r="68" s="50">
+      <c r="A68" s="47" t="inlineStr">
         <is>
           <t>API-180</t>
         </is>
       </c>
-      <c r="B72" s="41" t="inlineStr">
+      <c r="B68" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C72" s="42" t="inlineStr">
+      <c r="C68" s="42" t="inlineStr">
         <is>
           <t>/api/admin/community/reports</t>
         </is>
       </c>
-      <c r="D72" s="43" t="inlineStr">
+      <c r="D68" s="43" t="inlineStr">
         <is>
           <t>신고 처리</t>
         </is>
       </c>
-      <c r="E72" s="44" t="inlineStr">
+      <c r="E68" s="44" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F72" s="44" t="inlineStr">
+      <c r="F68" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G72" s="44" t="inlineStr">
+      <c r="G68" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H72" s="44" t="inlineStr">
+      <c r="H68" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I72" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J72" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K72" s="45" t="inlineStr">
+      <c r="I68" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J68" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L72" s="45" t="inlineStr">
+      <c r="L68" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M72" s="45" t="inlineStr">
+      <c r="M68" s="45" t="inlineStr">
         <is>
           <t>{
   "action*": "숨김|삭제|제재",
@@ -9477,7 +9070,7 @@
 }</t>
         </is>
       </c>
-      <c r="N72" s="45" t="inlineStr">
+      <c r="N68" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -9486,103 +9079,103 @@
 }</t>
         </is>
       </c>
-      <c r="O72" s="45" t="inlineStr"/>
-      <c r="P72" s="46" t="inlineStr">
+      <c r="O68" s="45" t="inlineStr"/>
+      <c r="P68" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q72" s="47" t="inlineStr"/>
-      <c r="R72" s="47" t="inlineStr">
+      <c r="Q68" s="47" t="inlineStr"/>
+      <c r="R68" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S72" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-COMM-01</t>
-        </is>
-      </c>
-      <c r="T72" s="47" t="inlineStr">
+      <c r="S68" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-MEMBER-01</t>
+        </is>
+      </c>
+      <c r="T68" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U72" s="48" t="n">
+      <c r="U68" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="73" s="50">
-      <c r="A73" s="47" t="inlineStr">
+    <row r="69" s="50">
+      <c r="A69" s="47" t="inlineStr">
         <is>
           <t>API-190</t>
         </is>
       </c>
-      <c r="B73" s="41" t="inlineStr">
+      <c r="B69" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C73" s="42" t="inlineStr">
+      <c r="C69" s="42" t="inlineStr">
         <is>
           <t>/api/admin/notifications/send</t>
         </is>
       </c>
-      <c r="D73" s="43" t="inlineStr">
+      <c r="D69" s="43" t="inlineStr">
         <is>
           <t>알림 발송</t>
         </is>
       </c>
-      <c r="E73" s="44" t="inlineStr">
+      <c r="E69" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F73" s="44" t="inlineStr">
+      <c r="F69" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G73" s="44" t="inlineStr">
+      <c r="G69" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H73" s="44" t="inlineStr">
+      <c r="H69" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I73" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J73" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K73" s="45" t="inlineStr">
+      <c r="I69" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J69" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L73" s="45" t="inlineStr">
+      <c r="L69" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M73" s="45" t="inlineStr">
+      <c r="M69" s="45" t="inlineStr">
         <is>
           <t>{
   "template*","segment*","payload":{}
 }</t>
         </is>
       </c>
-      <c r="N73" s="45" t="inlineStr">
+      <c r="N69" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -9592,101 +9185,101 @@
 data: { "queued":(int) }</t>
         </is>
       </c>
-      <c r="O73" s="45" t="inlineStr"/>
-      <c r="P73" s="46" t="inlineStr">
+      <c r="O69" s="45" t="inlineStr"/>
+      <c r="P69" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q73" s="47" t="inlineStr"/>
-      <c r="R73" s="47" t="inlineStr">
+      <c r="Q69" s="47" t="inlineStr"/>
+      <c r="R69" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005</t>
         </is>
       </c>
-      <c r="S73" s="47" t="inlineStr">
+      <c r="S69" s="47" t="inlineStr">
         <is>
           <t>ZB-A-NOTI-01</t>
         </is>
       </c>
-      <c r="T73" s="47" t="inlineStr">
+      <c r="T69" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U73" s="48" t="n">
+      <c r="U69" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="74" s="50">
-      <c r="A74" s="47" t="inlineStr">
+    <row r="70" s="50">
+      <c r="A70" s="47" t="inlineStr">
         <is>
           <t>API-195</t>
         </is>
       </c>
-      <c r="B74" s="41" t="inlineStr">
+      <c r="B70" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C74" s="42" t="inlineStr">
+      <c r="C70" s="42" t="inlineStr">
         <is>
           <t>/api/admin/stats</t>
         </is>
       </c>
-      <c r="D74" s="43" t="inlineStr">
+      <c r="D70" s="43" t="inlineStr">
         <is>
           <t>통계 리포트</t>
         </is>
       </c>
-      <c r="E74" s="44" t="inlineStr">
+      <c r="E70" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F74" s="44" t="inlineStr">
+      <c r="F70" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G74" s="44" t="inlineStr">
+      <c r="G70" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H74" s="44" t="inlineStr">
+      <c r="H70" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I74" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J74" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K74" s="45" t="inlineStr">
+      <c r="I70" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J70" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L74" s="45" t="inlineStr">
+      <c r="L70" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M74" s="45" t="inlineStr">
+      <c r="M70" s="45" t="inlineStr">
         <is>
           <t>?from=(date)&amp;to=(date)&amp;metric=(string)</t>
         </is>
       </c>
-      <c r="N74" s="45" t="inlineStr">
+      <c r="N70" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -9696,103 +9289,103 @@
 data: { "series":[] }</t>
         </is>
       </c>
-      <c r="O74" s="45" t="inlineStr"/>
-      <c r="P74" s="46" t="inlineStr">
+      <c r="O70" s="45" t="inlineStr"/>
+      <c r="P70" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q74" s="47" t="inlineStr"/>
-      <c r="R74" s="47" t="inlineStr">
+      <c r="Q70" s="47" t="inlineStr"/>
+      <c r="R70" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S74" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-STAT-01</t>
-        </is>
-      </c>
-      <c r="T74" s="47" t="inlineStr">
+      <c r="S70" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-NOTI-01</t>
+        </is>
+      </c>
+      <c r="T70" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U74" s="48" t="n">
+      <c r="U70" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="75" s="50">
-      <c r="A75" s="47" t="inlineStr">
+    <row r="71" s="50">
+      <c r="A71" s="47" t="inlineStr">
         <is>
           <t>API-199</t>
         </is>
       </c>
-      <c r="B75" s="41" t="inlineStr">
+      <c r="B71" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C75" s="42" t="inlineStr">
+      <c r="C71" s="42" t="inlineStr">
         <is>
           <t>/api/admin/roles</t>
         </is>
       </c>
-      <c r="D75" s="43" t="inlineStr">
+      <c r="D71" s="43" t="inlineStr">
         <is>
           <t>운영자/권한 관리</t>
         </is>
       </c>
-      <c r="E75" s="44" t="inlineStr">
+      <c r="E71" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F75" s="44" t="inlineStr">
+      <c r="F71" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G75" s="44" t="inlineStr">
+      <c r="G71" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H75" s="44" t="inlineStr">
+      <c r="H71" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I75" s="44" t="inlineStr">
+      <c r="I71" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="J75" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K75" s="45" t="inlineStr">
+      <c r="J71" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L75" s="45" t="inlineStr">
+      <c r="L71" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M75" s="45" t="inlineStr">
+      <c r="M71" s="45" t="inlineStr">
         <is>
           <t>{
   "userId*","role*","permissions":[]
 }</t>
         </is>
       </c>
-      <c r="N75" s="45" t="inlineStr">
+      <c r="N71" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -9801,109 +9394,109 @@
 }</t>
         </is>
       </c>
-      <c r="O75" s="45" t="inlineStr">
+      <c r="O71" s="45" t="inlineStr">
         <is>
           <t>RBAC·관리자만</t>
         </is>
       </c>
-      <c r="P75" s="46" t="inlineStr">
+      <c r="P71" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q75" s="47" t="inlineStr">
+      <c r="Q71" s="47" t="inlineStr">
         <is>
           <t>ITF-012</t>
         </is>
       </c>
-      <c r="R75" s="47" t="inlineStr">
+      <c r="R71" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S75" s="47" t="inlineStr">
+      <c r="S71" s="47" t="inlineStr">
         <is>
           <t>ZB-A-SYS-01</t>
         </is>
       </c>
-      <c r="T75" s="47" t="inlineStr">
+      <c r="T71" s="47" t="inlineStr">
         <is>
           <t>도출</t>
         </is>
       </c>
-      <c r="U75" s="48" t="n">
+      <c r="U71" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="76" s="50">
-      <c r="A76" s="47" t="inlineStr">
+    <row r="72" s="50">
+      <c r="A72" s="47" t="inlineStr">
         <is>
           <t>API-131</t>
         </is>
       </c>
-      <c r="B76" s="41" t="inlineStr">
+      <c r="B72" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C76" s="42" t="inlineStr">
+      <c r="C72" s="42" t="inlineStr">
         <is>
           <t>/api/admin/inspirations</t>
         </is>
       </c>
-      <c r="D76" s="43" t="inlineStr">
-        <is>
-          <t>인테리어 영감 목록</t>
-        </is>
-      </c>
-      <c r="E76" s="44" t="inlineStr">
+      <c r="D72" s="43" t="inlineStr">
+        <is>
+          <t>집구경(인테리어 영감) 목록</t>
+        </is>
+      </c>
+      <c r="E72" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F76" s="44" t="inlineStr">
+      <c r="F72" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G76" s="44" t="inlineStr">
+      <c r="G72" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H76" s="44" t="inlineStr">
+      <c r="H72" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I76" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J76" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K76" s="45" t="inlineStr">
+      <c r="I72" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J72" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L76" s="45" t="inlineStr">
+      <c r="L72" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M76" s="45" t="inlineStr">
+      <c r="M72" s="45" t="inlineStr">
         <is>
           <t>?space=(string)&amp;page=(int)</t>
         </is>
       </c>
-      <c r="N76" s="45" t="inlineStr">
+      <c r="N72" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -9913,107 +9506,107 @@
 data: { "items":[], "page","totalCount" }</t>
         </is>
       </c>
-      <c r="O76" s="45" t="inlineStr"/>
-      <c r="P76" s="46" t="inlineStr">
+      <c r="O72" s="45" t="inlineStr"/>
+      <c r="P72" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q76" s="47" t="inlineStr">
+      <c r="Q72" s="47" t="inlineStr">
         <is>
           <t>ITF-009</t>
         </is>
       </c>
-      <c r="R76" s="47" t="inlineStr">
+      <c r="R72" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S76" s="47" t="inlineStr">
+      <c r="S72" s="47" t="inlineStr">
         <is>
           <t>ZB-A-TOUR-01</t>
         </is>
       </c>
-      <c r="T76" s="47" t="inlineStr">
+      <c r="T72" s="47" t="inlineStr">
         <is>
           <t>도출·검토보완</t>
         </is>
       </c>
-      <c r="U76" s="48" t="n">
+      <c r="U72" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="77" s="50">
-      <c r="A77" s="47" t="inlineStr">
+    <row r="73" s="50">
+      <c r="A73" s="47" t="inlineStr">
         <is>
           <t>API-132</t>
         </is>
       </c>
-      <c r="B77" s="41" t="inlineStr">
+      <c r="B73" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C77" s="42" t="inlineStr">
+      <c r="C73" s="42" t="inlineStr">
         <is>
           <t>/api/admin/inspirations/{id}</t>
         </is>
       </c>
-      <c r="D77" s="43" t="inlineStr">
-        <is>
-          <t>인테리어 영감 수정</t>
-        </is>
-      </c>
-      <c r="E77" s="44" t="inlineStr">
+      <c r="D73" s="43" t="inlineStr">
+        <is>
+          <t>집구경(인테리어 영감) 수정</t>
+        </is>
+      </c>
+      <c r="E73" s="44" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F77" s="44" t="inlineStr">
+      <c r="F73" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G77" s="44" t="inlineStr">
+      <c r="G73" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H77" s="44" t="inlineStr">
+      <c r="H73" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I77" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J77" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K77" s="45" t="inlineStr">
+      <c r="I73" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J73" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L77" s="45" t="inlineStr">
+      <c r="L73" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M77" s="45" t="inlineStr">
+      <c r="M73" s="45" t="inlineStr">
         <is>
           <t>{
   "space","image","taggedProducts":[]
 }</t>
         </is>
       </c>
-      <c r="N77" s="45" t="inlineStr">
+      <c r="N73" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -10022,105 +9615,105 @@
 }</t>
         </is>
       </c>
-      <c r="O77" s="45" t="inlineStr"/>
-      <c r="P77" s="46" t="inlineStr">
+      <c r="O73" s="45" t="inlineStr"/>
+      <c r="P73" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q77" s="47" t="inlineStr">
+      <c r="Q73" s="47" t="inlineStr">
         <is>
           <t>ITF-009</t>
         </is>
       </c>
-      <c r="R77" s="47" t="inlineStr">
+      <c r="R73" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S77" s="47" t="inlineStr">
+      <c r="S73" s="47" t="inlineStr">
         <is>
           <t>ZB-A-TOUR-01</t>
         </is>
       </c>
-      <c r="T77" s="47" t="inlineStr">
+      <c r="T73" s="47" t="inlineStr">
         <is>
           <t>도출·검토보완</t>
         </is>
       </c>
-      <c r="U77" s="48" t="n">
+      <c r="U73" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="78" s="50">
-      <c r="A78" s="47" t="inlineStr">
+    <row r="74" s="50">
+      <c r="A74" s="47" t="inlineStr">
         <is>
           <t>API-133</t>
         </is>
       </c>
-      <c r="B78" s="41" t="inlineStr">
+      <c r="B74" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C78" s="42" t="inlineStr">
+      <c r="C74" s="42" t="inlineStr">
         <is>
           <t>/api/admin/inspirations/{id}</t>
         </is>
       </c>
-      <c r="D78" s="43" t="inlineStr">
-        <is>
-          <t>인테리어 영감 삭제</t>
-        </is>
-      </c>
-      <c r="E78" s="44" t="inlineStr">
+      <c r="D74" s="43" t="inlineStr">
+        <is>
+          <t>집구경(인테리어 영감) 삭제</t>
+        </is>
+      </c>
+      <c r="E74" s="44" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="F78" s="44" t="inlineStr">
+      <c r="F74" s="44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G78" s="44" t="inlineStr">
+      <c r="G74" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H78" s="44" t="inlineStr">
+      <c r="H74" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I78" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J78" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K78" s="45" t="inlineStr">
+      <c r="I74" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J74" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L78" s="45" t="inlineStr">
+      <c r="L74" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M78" s="45" t="inlineStr">
+      <c r="M74" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N78" s="45" t="inlineStr">
+      <c r="N74" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -10129,101 +9722,101 @@
 }</t>
         </is>
       </c>
-      <c r="O78" s="45" t="inlineStr"/>
-      <c r="P78" s="46" t="inlineStr">
+      <c r="O74" s="45" t="inlineStr"/>
+      <c r="P74" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q78" s="47" t="inlineStr"/>
-      <c r="R78" s="47" t="inlineStr">
+      <c r="Q74" s="47" t="inlineStr"/>
+      <c r="R74" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S78" s="47" t="inlineStr">
+      <c r="S74" s="47" t="inlineStr">
         <is>
           <t>ZB-A-TOUR-01</t>
         </is>
       </c>
-      <c r="T78" s="47" t="inlineStr">
+      <c r="T74" s="47" t="inlineStr">
         <is>
           <t>도출·검토보완</t>
         </is>
       </c>
-      <c r="U78" s="48" t="n">
+      <c r="U74" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="79" s="50">
-      <c r="A79" s="47" t="inlineStr">
-        <is>
-          <t>API-141</t>
-        </is>
-      </c>
-      <c r="B79" s="41" t="inlineStr">
+    <row r="75" s="50">
+      <c r="A75" s="47" t="inlineStr">
+        <is>
+          <t>API-151</t>
+        </is>
+      </c>
+      <c r="B75" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C79" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/showrooms</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="inlineStr">
-        <is>
-          <t>쇼룸 목록</t>
-        </is>
-      </c>
-      <c r="E79" s="44" t="inlineStr">
+      <c r="C75" s="42" t="inlineStr">
+        <is>
+          <t>/api/admin/products</t>
+        </is>
+      </c>
+      <c r="D75" s="43" t="inlineStr">
+        <is>
+          <t>상품 목록(2차)</t>
+        </is>
+      </c>
+      <c r="E75" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F79" s="44" t="inlineStr">
+      <c r="F75" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G79" s="44" t="inlineStr">
+      <c r="G75" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H79" s="44" t="inlineStr">
+      <c r="H75" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I79" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J79" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K79" s="45" t="inlineStr">
+      <c r="I75" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L79" s="45" t="inlineStr">
+      <c r="L75" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M79" s="45" t="inlineStr">
-        <is>
-          <t>?page=(int)</t>
-        </is>
-      </c>
-      <c r="N79" s="45" t="inlineStr">
+      <c r="M75" s="45" t="inlineStr">
+        <is>
+          <t>?category=(string)&amp;page=(int)</t>
+        </is>
+      </c>
+      <c r="N75" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -10233,103 +9826,111 @@
 data: { "items":[] }</t>
         </is>
       </c>
-      <c r="O79" s="45" t="inlineStr"/>
-      <c r="P79" s="46" t="inlineStr">
+      <c r="O75" s="45" t="inlineStr">
+        <is>
+          <t>2차</t>
+        </is>
+      </c>
+      <c r="P75" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q79" s="47" t="inlineStr"/>
-      <c r="R79" s="47" t="inlineStr">
+      <c r="Q75" s="47" t="inlineStr">
+        <is>
+          <t>ITF-007</t>
+        </is>
+      </c>
+      <c r="R75" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S79" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOW-01</t>
-        </is>
-      </c>
-      <c r="T79" s="47" t="inlineStr">
-        <is>
-          <t>도출·검토보완</t>
-        </is>
-      </c>
-      <c r="U79" s="48" t="n">
+      <c r="S75" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SHOP-01</t>
+        </is>
+      </c>
+      <c r="T75" s="47" t="inlineStr">
+        <is>
+          <t>도출·2차·검토보완</t>
+        </is>
+      </c>
+      <c r="U75" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="80" s="50">
-      <c r="A80" s="47" t="inlineStr">
-        <is>
-          <t>API-142</t>
-        </is>
-      </c>
-      <c r="B80" s="41" t="inlineStr">
+    <row r="76" s="50">
+      <c r="A76" s="47" t="inlineStr">
+        <is>
+          <t>API-152</t>
+        </is>
+      </c>
+      <c r="B76" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C80" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/showrooms/{id}</t>
-        </is>
-      </c>
-      <c r="D80" s="43" t="inlineStr">
-        <is>
-          <t>쇼룸 수정</t>
-        </is>
-      </c>
-      <c r="E80" s="44" t="inlineStr">
+      <c r="C76" s="42" t="inlineStr">
+        <is>
+          <t>/api/admin/products/{id}</t>
+        </is>
+      </c>
+      <c r="D76" s="43" t="inlineStr">
+        <is>
+          <t>상품 수정(2차)</t>
+        </is>
+      </c>
+      <c r="E76" s="44" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F80" s="44" t="inlineStr">
+      <c r="F76" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G80" s="44" t="inlineStr">
+      <c r="G76" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H80" s="44" t="inlineStr">
+      <c r="H76" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I80" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J80" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K80" s="45" t="inlineStr">
+      <c r="I76" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J76" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L80" s="45" t="inlineStr">
+      <c r="L76" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M80" s="45" t="inlineStr">
+      <c r="M76" s="45" t="inlineStr">
         <is>
           <t>{
-  "name","address","lat","lng","slots":[]
+  "name","price","stock","exposed":(boolean)
 }</t>
         </is>
       </c>
-      <c r="N80" s="45" t="inlineStr">
+      <c r="N76" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -10338,101 +9939,105 @@
 }</t>
         </is>
       </c>
-      <c r="O80" s="45" t="inlineStr"/>
-      <c r="P80" s="46" t="inlineStr">
+      <c r="O76" s="45" t="inlineStr">
+        <is>
+          <t>2차</t>
+        </is>
+      </c>
+      <c r="P76" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q80" s="47" t="inlineStr"/>
-      <c r="R80" s="47" t="inlineStr">
+      <c r="Q76" s="47" t="inlineStr"/>
+      <c r="R76" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S80" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOW-01</t>
-        </is>
-      </c>
-      <c r="T80" s="47" t="inlineStr">
-        <is>
-          <t>도출·검토보완</t>
-        </is>
-      </c>
-      <c r="U80" s="48" t="n">
+      <c r="S76" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SHOP-01</t>
+        </is>
+      </c>
+      <c r="T76" s="47" t="inlineStr">
+        <is>
+          <t>도출·2차·검토보완</t>
+        </is>
+      </c>
+      <c r="U76" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="81" s="50">
-      <c r="A81" s="47" t="inlineStr">
-        <is>
-          <t>API-143</t>
-        </is>
-      </c>
-      <c r="B81" s="41" t="inlineStr">
+    <row r="77" s="50">
+      <c r="A77" s="47" t="inlineStr">
+        <is>
+          <t>API-153</t>
+        </is>
+      </c>
+      <c r="B77" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C81" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/showrooms/{id}</t>
-        </is>
-      </c>
-      <c r="D81" s="43" t="inlineStr">
-        <is>
-          <t>쇼룸 삭제</t>
-        </is>
-      </c>
-      <c r="E81" s="44" t="inlineStr">
+      <c r="C77" s="42" t="inlineStr">
+        <is>
+          <t>/api/admin/products/{id}</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>상품 삭제(2차)</t>
+        </is>
+      </c>
+      <c r="E77" s="44" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="F81" s="44" t="inlineStr">
+      <c r="F77" s="44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G81" s="44" t="inlineStr">
+      <c r="G77" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H81" s="44" t="inlineStr">
+      <c r="H77" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I81" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J81" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K81" s="45" t="inlineStr">
+      <c r="I77" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J77" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L81" s="45" t="inlineStr">
+      <c r="L77" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M81" s="45" t="inlineStr">
+      <c r="M77" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N81" s="45" t="inlineStr">
+      <c r="N77" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -10441,429 +10046,105 @@
 }</t>
         </is>
       </c>
-      <c r="O81" s="45" t="inlineStr"/>
-      <c r="P81" s="46" t="inlineStr">
+      <c r="O77" s="45" t="inlineStr">
+        <is>
+          <t>2차</t>
+        </is>
+      </c>
+      <c r="P77" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q81" s="47" t="inlineStr"/>
-      <c r="R81" s="47" t="inlineStr">
+      <c r="Q77" s="47" t="inlineStr"/>
+      <c r="R77" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S81" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOW-01</t>
-        </is>
-      </c>
-      <c r="T81" s="47" t="inlineStr">
-        <is>
-          <t>도출·검토보완</t>
-        </is>
-      </c>
-      <c r="U81" s="48" t="n">
+      <c r="S77" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SHOP-01</t>
+        </is>
+      </c>
+      <c r="T77" s="47" t="inlineStr">
+        <is>
+          <t>도출·2차·검토보완</t>
+        </is>
+      </c>
+      <c r="U77" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="82" s="50">
-      <c r="A82" s="47" t="inlineStr">
-        <is>
-          <t>API-151</t>
-        </is>
-      </c>
-      <c r="B82" s="41" t="inlineStr">
+    <row r="78" s="50">
+      <c r="A78" s="47" t="inlineStr">
+        <is>
+          <t>API-156</t>
+        </is>
+      </c>
+      <c r="B78" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C82" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/products</t>
-        </is>
-      </c>
-      <c r="D82" s="43" t="inlineStr">
-        <is>
-          <t>상품 목록(2차)</t>
-        </is>
-      </c>
-      <c r="E82" s="44" t="inlineStr">
+      <c r="C78" s="42" t="inlineStr">
+        <is>
+          <t>/api/admin/categories</t>
+        </is>
+      </c>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>카테고리/브랜드 목록(2차)</t>
+        </is>
+      </c>
+      <c r="E78" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F82" s="44" t="inlineStr">
+      <c r="F78" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G82" s="44" t="inlineStr">
+      <c r="G78" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H82" s="44" t="inlineStr">
+      <c r="H78" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I82" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J82" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K82" s="45" t="inlineStr">
+      <c r="I78" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J78" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L82" s="45" t="inlineStr">
+      <c r="L78" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M82" s="45" t="inlineStr">
-        <is>
-          <t>?category=(string)&amp;page=(int)</t>
-        </is>
-      </c>
-      <c r="N82" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "success": (boolean),
-  "data": (object|null),
-  "error": (object|null)
-}
-data: { "items":[] }</t>
-        </is>
-      </c>
-      <c r="O82" s="45" t="inlineStr">
-        <is>
-          <t>2차</t>
-        </is>
-      </c>
-      <c r="P82" s="46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q82" s="47" t="inlineStr">
-        <is>
-          <t>ITF-007</t>
-        </is>
-      </c>
-      <c r="R82" s="47" t="inlineStr">
-        <is>
-          <t>ERR-003</t>
-        </is>
-      </c>
-      <c r="S82" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOP-01</t>
-        </is>
-      </c>
-      <c r="T82" s="47" t="inlineStr">
-        <is>
-          <t>도출·2차·검토보완</t>
-        </is>
-      </c>
-      <c r="U82" s="48" t="n">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="83" s="50">
-      <c r="A83" s="47" t="inlineStr">
-        <is>
-          <t>API-152</t>
-        </is>
-      </c>
-      <c r="B83" s="41" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="C83" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/products/{id}</t>
-        </is>
-      </c>
-      <c r="D83" s="43" t="inlineStr">
-        <is>
-          <t>상품 수정(2차)</t>
-        </is>
-      </c>
-      <c r="E83" s="44" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F83" s="44" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G83" s="44" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H83" s="44" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I83" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J83" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K83" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Authorization: Bearer {accessToken}</t>
-        </is>
-      </c>
-      <c r="L83" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Date: (표준)</t>
-        </is>
-      </c>
-      <c r="M83" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "name","price","stock","exposed":(boolean)
-}</t>
-        </is>
-      </c>
-      <c r="N83" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "success": (boolean),
-  "data": (object|null),
-  "error": (object|null)
-}</t>
-        </is>
-      </c>
-      <c r="O83" s="45" t="inlineStr">
-        <is>
-          <t>2차</t>
-        </is>
-      </c>
-      <c r="P83" s="46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q83" s="47" t="inlineStr"/>
-      <c r="R83" s="47" t="inlineStr">
-        <is>
-          <t>ERR-003,ERR-008</t>
-        </is>
-      </c>
-      <c r="S83" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOP-01</t>
-        </is>
-      </c>
-      <c r="T83" s="47" t="inlineStr">
-        <is>
-          <t>도출·2차·검토보완</t>
-        </is>
-      </c>
-      <c r="U83" s="48" t="n">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="84" s="50">
-      <c r="A84" s="47" t="inlineStr">
-        <is>
-          <t>API-153</t>
-        </is>
-      </c>
-      <c r="B84" s="41" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="C84" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/products/{id}</t>
-        </is>
-      </c>
-      <c r="D84" s="43" t="inlineStr">
-        <is>
-          <t>상품 삭제(2차)</t>
-        </is>
-      </c>
-      <c r="E84" s="44" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="F84" s="44" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G84" s="44" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H84" s="44" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I84" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J84" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K84" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Authorization: Bearer {accessToken}</t>
-        </is>
-      </c>
-      <c r="L84" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Date: (표준)</t>
-        </is>
-      </c>
-      <c r="M84" s="45" t="inlineStr">
+      <c r="M78" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N84" s="45" t="inlineStr">
-        <is>
-          <t>{
-  "success": (boolean),
-  "data": (object|null),
-  "error": (object|null)
-}</t>
-        </is>
-      </c>
-      <c r="O84" s="45" t="inlineStr">
-        <is>
-          <t>2차</t>
-        </is>
-      </c>
-      <c r="P84" s="46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q84" s="47" t="inlineStr"/>
-      <c r="R84" s="47" t="inlineStr">
-        <is>
-          <t>ERR-003,ERR-008</t>
-        </is>
-      </c>
-      <c r="S84" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOP-01</t>
-        </is>
-      </c>
-      <c r="T84" s="47" t="inlineStr">
-        <is>
-          <t>도출·2차·검토보완</t>
-        </is>
-      </c>
-      <c r="U84" s="48" t="n">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="85" s="50">
-      <c r="A85" s="47" t="inlineStr">
-        <is>
-          <t>API-156</t>
-        </is>
-      </c>
-      <c r="B85" s="41" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="C85" s="42" t="inlineStr">
-        <is>
-          <t>/api/admin/categories</t>
-        </is>
-      </c>
-      <c r="D85" s="43" t="inlineStr">
-        <is>
-          <t>카테고리/브랜드 목록(2차)</t>
-        </is>
-      </c>
-      <c r="E85" s="44" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F85" s="44" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G85" s="44" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H85" s="44" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I85" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J85" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K85" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Authorization: Bearer {accessToken}</t>
-        </is>
-      </c>
-      <c r="L85" s="45" t="inlineStr">
-        <is>
-          <t>• Content-Type: application/json
-• Date: (표준)</t>
-        </is>
-      </c>
-      <c r="M85" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="45" t="inlineStr">
+      <c r="N78" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -10873,104 +10154,104 @@
 data: { "categories":[], "brands":[] }</t>
         </is>
       </c>
-      <c r="O85" s="45" t="inlineStr">
+      <c r="O78" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P85" s="46" t="inlineStr">
+      <c r="P78" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q85" s="47" t="inlineStr">
+      <c r="Q78" s="47" t="inlineStr">
         <is>
           <t>ITF-007</t>
         </is>
       </c>
-      <c r="R85" s="47" t="inlineStr">
+      <c r="R78" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S85" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOP-02</t>
-        </is>
-      </c>
-      <c r="T85" s="47" t="inlineStr">
+      <c r="S78" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SHOP-01</t>
+        </is>
+      </c>
+      <c r="T78" s="47" t="inlineStr">
         <is>
           <t>도출·2차·검토보완</t>
         </is>
       </c>
-      <c r="U85" s="48" t="n">
+      <c r="U78" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="86" s="50">
-      <c r="A86" s="47" t="inlineStr">
+    <row r="79" s="50">
+      <c r="A79" s="47" t="inlineStr">
         <is>
           <t>API-157</t>
         </is>
       </c>
-      <c r="B86" s="41" t="inlineStr">
+      <c r="B79" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C86" s="42" t="inlineStr">
+      <c r="C79" s="42" t="inlineStr">
         <is>
           <t>/api/admin/categories</t>
         </is>
       </c>
-      <c r="D86" s="43" t="inlineStr">
+      <c r="D79" s="43" t="inlineStr">
         <is>
           <t>카테고리/브랜드 등록(2차)</t>
         </is>
       </c>
-      <c r="E86" s="44" t="inlineStr">
+      <c r="E79" s="44" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F86" s="44" t="inlineStr">
+      <c r="F79" s="44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G86" s="44" t="inlineStr">
+      <c r="G79" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H86" s="44" t="inlineStr">
+      <c r="H79" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I86" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J86" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K86" s="45" t="inlineStr">
+      <c r="I79" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J79" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L86" s="45" t="inlineStr">
+      <c r="L79" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M86" s="45" t="inlineStr">
+      <c r="M79" s="45" t="inlineStr">
         <is>
           <t>{
   "type*": "category|brand",
@@ -10978,7 +10259,7 @@
 }</t>
         </is>
       </c>
-      <c r="N86" s="45" t="inlineStr">
+      <c r="N79" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -10987,107 +10268,107 @@
 }</t>
         </is>
       </c>
-      <c r="O86" s="45" t="inlineStr">
+      <c r="O79" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P86" s="46" t="inlineStr">
+      <c r="P79" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q86" s="47" t="inlineStr"/>
-      <c r="R86" s="47" t="inlineStr">
+      <c r="Q79" s="47" t="inlineStr"/>
+      <c r="R79" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-005</t>
         </is>
       </c>
-      <c r="S86" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOP-02</t>
-        </is>
-      </c>
-      <c r="T86" s="47" t="inlineStr">
+      <c r="S79" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SHOP-01</t>
+        </is>
+      </c>
+      <c r="T79" s="47" t="inlineStr">
         <is>
           <t>도출·2차·검토보완</t>
         </is>
       </c>
-      <c r="U86" s="48" t="n">
+      <c r="U79" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="87" s="50">
-      <c r="A87" s="47" t="inlineStr">
+    <row r="80" s="50">
+      <c r="A80" s="47" t="inlineStr">
         <is>
           <t>API-158</t>
         </is>
       </c>
-      <c r="B87" s="41" t="inlineStr">
+      <c r="B80" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C87" s="42" t="inlineStr">
+      <c r="C80" s="42" t="inlineStr">
         <is>
           <t>/api/admin/categories/{id}</t>
         </is>
       </c>
-      <c r="D87" s="43" t="inlineStr">
+      <c r="D80" s="43" t="inlineStr">
         <is>
           <t>카테고리/브랜드 수정(2차)</t>
         </is>
       </c>
-      <c r="E87" s="44" t="inlineStr">
+      <c r="E80" s="44" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F87" s="44" t="inlineStr">
+      <c r="F80" s="44" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G87" s="44" t="inlineStr">
+      <c r="G80" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H87" s="44" t="inlineStr">
+      <c r="H80" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I87" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J87" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K87" s="45" t="inlineStr">
+      <c r="I80" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J80" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L87" s="45" t="inlineStr">
+      <c r="L80" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M87" s="45" t="inlineStr">
+      <c r="M80" s="45" t="inlineStr">
         <is>
           <t>{
   "name*": (string)
 }</t>
         </is>
       </c>
-      <c r="N87" s="45" t="inlineStr">
+      <c r="N80" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -11096,105 +10377,105 @@
 }</t>
         </is>
       </c>
-      <c r="O87" s="45" t="inlineStr">
+      <c r="O80" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P87" s="46" t="inlineStr">
+      <c r="P80" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q87" s="47" t="inlineStr"/>
-      <c r="R87" s="47" t="inlineStr">
+      <c r="Q80" s="47" t="inlineStr"/>
+      <c r="R80" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S87" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOP-02</t>
-        </is>
-      </c>
-      <c r="T87" s="47" t="inlineStr">
+      <c r="S80" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SHOP-01</t>
+        </is>
+      </c>
+      <c r="T80" s="47" t="inlineStr">
         <is>
           <t>도출·2차·검토보완</t>
         </is>
       </c>
-      <c r="U87" s="48" t="n">
+      <c r="U80" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="88" s="50">
-      <c r="A88" s="47" t="inlineStr">
+    <row r="81" s="50">
+      <c r="A81" s="47" t="inlineStr">
         <is>
           <t>API-159</t>
         </is>
       </c>
-      <c r="B88" s="41" t="inlineStr">
+      <c r="B81" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C88" s="42" t="inlineStr">
+      <c r="C81" s="42" t="inlineStr">
         <is>
           <t>/api/admin/categories/{id}</t>
         </is>
       </c>
-      <c r="D88" s="43" t="inlineStr">
+      <c r="D81" s="43" t="inlineStr">
         <is>
           <t>카테고리/브랜드 삭제(2차)</t>
         </is>
       </c>
-      <c r="E88" s="44" t="inlineStr">
+      <c r="E81" s="44" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="F88" s="44" t="inlineStr">
+      <c r="F81" s="44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G88" s="44" t="inlineStr">
+      <c r="G81" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H88" s="44" t="inlineStr">
+      <c r="H81" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I88" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J88" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K88" s="45" t="inlineStr">
+      <c r="I81" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J81" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L88" s="45" t="inlineStr">
+      <c r="L81" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M88" s="45" t="inlineStr">
+      <c r="M81" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N88" s="45" t="inlineStr">
+      <c r="N81" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -11203,105 +10484,105 @@
 }</t>
         </is>
       </c>
-      <c r="O88" s="45" t="inlineStr">
+      <c r="O81" s="45" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="P88" s="46" t="inlineStr">
+      <c r="P81" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q88" s="47" t="inlineStr"/>
-      <c r="R88" s="47" t="inlineStr">
+      <c r="Q81" s="47" t="inlineStr"/>
+      <c r="R81" s="47" t="inlineStr">
         <is>
           <t>ERR-003,ERR-008</t>
         </is>
       </c>
-      <c r="S88" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOP-02</t>
-        </is>
-      </c>
-      <c r="T88" s="47" t="inlineStr">
+      <c r="S81" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SHOP-01</t>
+        </is>
+      </c>
+      <c r="T81" s="47" t="inlineStr">
         <is>
           <t>도출·2차·검토보완</t>
         </is>
       </c>
-      <c r="U88" s="48" t="n">
+      <c r="U81" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="89" s="50">
-      <c r="A89" s="47" t="inlineStr">
+    <row r="82" s="50">
+      <c r="A82" s="47" t="inlineStr">
         <is>
           <t>API-181</t>
         </is>
       </c>
-      <c r="B89" s="41" t="inlineStr">
+      <c r="B82" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C89" s="42" t="inlineStr">
+      <c r="C82" s="42" t="inlineStr">
         <is>
           <t>/api/admin/community/reports</t>
         </is>
       </c>
-      <c r="D89" s="43" t="inlineStr">
+      <c r="D82" s="43" t="inlineStr">
         <is>
           <t>신고 목록</t>
         </is>
       </c>
-      <c r="E89" s="44" t="inlineStr">
+      <c r="E82" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F89" s="44" t="inlineStr">
+      <c r="F82" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G89" s="44" t="inlineStr">
+      <c r="G82" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H89" s="44" t="inlineStr">
+      <c r="H82" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I89" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J89" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K89" s="45" t="inlineStr">
+      <c r="I82" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J82" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L89" s="45" t="inlineStr">
+      <c r="L82" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M89" s="45" t="inlineStr">
+      <c r="M82" s="45" t="inlineStr">
         <is>
           <t>?status=(string)&amp;page=(int)</t>
         </is>
       </c>
-      <c r="N89" s="45" t="inlineStr">
+      <c r="N82" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -11311,109 +10592,109 @@
 data: { "items":[ {"reportId","targetId","reason","status"} ] }</t>
         </is>
       </c>
-      <c r="O89" s="45" t="inlineStr">
+      <c r="O82" s="45" t="inlineStr">
         <is>
           <t>신고 처리 큐</t>
         </is>
       </c>
-      <c r="P89" s="46" t="inlineStr">
+      <c r="P82" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q89" s="47" t="inlineStr">
+      <c r="Q82" s="47" t="inlineStr">
         <is>
           <t>ITF-008</t>
         </is>
       </c>
-      <c r="R89" s="47" t="inlineStr">
+      <c r="R82" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S89" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-COMM-01</t>
-        </is>
-      </c>
-      <c r="T89" s="47" t="inlineStr">
+      <c r="S82" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-MEMBER-01</t>
+        </is>
+      </c>
+      <c r="T82" s="47" t="inlineStr">
         <is>
           <t>도출·검토보완</t>
         </is>
       </c>
-      <c r="U89" s="48" t="n">
+      <c r="U82" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="90" s="50">
-      <c r="A90" s="47" t="inlineStr">
+    <row r="83" s="50">
+      <c r="A83" s="47" t="inlineStr">
         <is>
           <t>API-191</t>
         </is>
       </c>
-      <c r="B90" s="41" t="inlineStr">
+      <c r="B83" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C90" s="42" t="inlineStr">
+      <c r="C83" s="42" t="inlineStr">
         <is>
           <t>/api/admin/notifications</t>
         </is>
       </c>
-      <c r="D90" s="43" t="inlineStr">
+      <c r="D83" s="43" t="inlineStr">
         <is>
           <t>알림 발송 이력/템플릿</t>
         </is>
       </c>
-      <c r="E90" s="44" t="inlineStr">
+      <c r="E83" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F90" s="44" t="inlineStr">
+      <c r="F83" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G90" s="44" t="inlineStr">
+      <c r="G83" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H90" s="44" t="inlineStr">
+      <c r="H83" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I90" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J90" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K90" s="45" t="inlineStr">
+      <c r="I83" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J83" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L90" s="45" t="inlineStr">
+      <c r="L83" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M90" s="45" t="inlineStr">
+      <c r="M83" s="45" t="inlineStr">
         <is>
           <t>?page=(int)</t>
         </is>
       </c>
-      <c r="N90" s="45" t="inlineStr">
+      <c r="N83" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -11423,101 +10704,101 @@
 data: { "history":[], "templates":[] }</t>
         </is>
       </c>
-      <c r="O90" s="45" t="inlineStr"/>
-      <c r="P90" s="46" t="inlineStr">
+      <c r="O83" s="45" t="inlineStr"/>
+      <c r="P83" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q90" s="47" t="inlineStr"/>
-      <c r="R90" s="47" t="inlineStr">
+      <c r="Q83" s="47" t="inlineStr"/>
+      <c r="R83" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S90" s="47" t="inlineStr">
+      <c r="S83" s="47" t="inlineStr">
         <is>
           <t>ZB-A-NOTI-01</t>
         </is>
       </c>
-      <c r="T90" s="47" t="inlineStr">
+      <c r="T83" s="47" t="inlineStr">
         <is>
           <t>도출·검토보완</t>
         </is>
       </c>
-      <c r="U90" s="48" t="n">
+      <c r="U83" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="91" s="50">
-      <c r="A91" s="47" t="inlineStr">
+    <row r="84" s="50">
+      <c r="A84" s="47" t="inlineStr">
         <is>
           <t>API-192</t>
         </is>
       </c>
-      <c r="B91" s="41" t="inlineStr">
+      <c r="B84" s="41" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C91" s="42" t="inlineStr">
+      <c r="C84" s="42" t="inlineStr">
         <is>
           <t>/api/admin/audit-logs</t>
         </is>
       </c>
-      <c r="D91" s="43" t="inlineStr">
+      <c r="D84" s="43" t="inlineStr">
         <is>
           <t>관리자 활동 감사 로그</t>
         </is>
       </c>
-      <c r="E91" s="44" t="inlineStr">
+      <c r="E84" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F91" s="44" t="inlineStr">
+      <c r="F84" s="44" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G91" s="44" t="inlineStr">
+      <c r="G84" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="H91" s="44" t="inlineStr">
+      <c r="H84" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="I91" s="44" t="inlineStr">
+      <c r="I84" s="44" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="J91" s="44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K91" s="45" t="inlineStr">
+      <c r="J84" s="44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Authorization: Bearer {accessToken}</t>
         </is>
       </c>
-      <c r="L91" s="45" t="inlineStr">
+      <c r="L84" s="45" t="inlineStr">
         <is>
           <t>• Content-Type: application/json
 • Date: (표준)</t>
         </is>
       </c>
-      <c r="M91" s="45" t="inlineStr">
+      <c r="M84" s="45" t="inlineStr">
         <is>
           <t>?actor=(string)&amp;from=(date)&amp;to=(date)&amp;page=(int)</t>
         </is>
       </c>
-      <c r="N91" s="45" t="inlineStr">
+      <c r="N84" s="45" t="inlineStr">
         <is>
           <t>{
   "success": (boolean),
@@ -11527,40 +10808,47 @@
 data: { "items":[ {"actor","action","target","at","ip"} ], "page","totalCount" }</t>
         </is>
       </c>
-      <c r="O91" s="45" t="inlineStr">
+      <c r="O84" s="45" t="inlineStr">
         <is>
           <t>불변 감사 로그(관리자만)</t>
         </is>
       </c>
-      <c r="P91" s="46" t="inlineStr">
+      <c r="P84" s="46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q91" s="47" t="inlineStr">
+      <c r="Q84" s="47" t="inlineStr">
         <is>
           <t>ITF-012</t>
         </is>
       </c>
-      <c r="R91" s="47" t="inlineStr">
+      <c r="R84" s="47" t="inlineStr">
         <is>
           <t>ERR-003</t>
         </is>
       </c>
-      <c r="S91" s="47" t="inlineStr">
-        <is>
-          <t>ZB-A-SYS-02</t>
-        </is>
-      </c>
-      <c r="T91" s="47" t="inlineStr">
+      <c r="S84" s="47" t="inlineStr">
+        <is>
+          <t>ZB-A-SYS-01</t>
+        </is>
+      </c>
+      <c r="T84" s="47" t="inlineStr">
         <is>
           <t>도출·검토보완</t>
         </is>
       </c>
-      <c r="U91" s="48" t="n">
+      <c r="U84" s="48" t="n">
         <v>46230</v>
       </c>
     </row>
+    <row r="85" s="50"/>
+    <row r="86" s="50"/>
+    <row r="87" s="50"/>
+    <row r="88" s="50"/>
+    <row r="89" s="50"/>
+    <row r="90" s="50"/>
+    <row r="91" s="50"/>
     <row r="92" s="50"/>
     <row r="93" s="50"/>
     <row r="94" s="50"/>

--- a/docs/ZIPBODA_API 및 인터페이스 정의서_v0.1.xlsx
+++ b/docs/ZIPBODA_API 및 인터페이스 정의서_v0.1.xlsx
@@ -869,11 +869,23 @@
       <c r="F6" s="21" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="50">
-      <c r="A7" s="21" t="n"/>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="24" t="n"/>
+      <c r="A7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>admin 화면 통합 정합 — 연관화면 갱신(API-111/112→SUBS-01, 121/122→PLAN-01, 160/161→SHOP-01)</t>
+        </is>
+      </c>
       <c r="D7" s="21" t="n"/>
-      <c r="E7" s="30" t="n"/>
+      <c r="E7" s="30" t="n">
+        <v>46234</v>
+      </c>
       <c r="F7" s="21" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="50">
@@ -7674,7 +7686,7 @@
       </c>
       <c r="S55" s="47" t="inlineStr">
         <is>
-          <t>ZB-A-SUBS-02</t>
+          <t>ZB-A-SUBS-01</t>
         </is>
       </c>
       <c r="T55" s="47" t="inlineStr">
@@ -7779,7 +7791,7 @@
       </c>
       <c r="S56" s="47" t="inlineStr">
         <is>
-          <t>ZB-A-SUBS-02</t>
+          <t>ZB-A-SUBS-01</t>
         </is>
       </c>
       <c r="T56" s="47" t="inlineStr">
@@ -8209,7 +8221,7 @@
       </c>
       <c r="S60" s="47" t="inlineStr">
         <is>
-          <t>ZB-A-PLAN-02</t>
+          <t>ZB-A-PLAN-01</t>
         </is>
       </c>
       <c r="T60" s="47" t="inlineStr">
@@ -8319,7 +8331,7 @@
       </c>
       <c r="S61" s="47" t="inlineStr">
         <is>
-          <t>ZB-A-PLAN-02</t>
+          <t>ZB-A-PLAN-01</t>
         </is>
       </c>
       <c r="T61" s="47" t="inlineStr">
@@ -8657,7 +8669,7 @@
       </c>
       <c r="S64" s="47" t="inlineStr">
         <is>
-          <t>ZB-A-ORDER-01</t>
+          <t>ZB-A-SHOP-01</t>
         </is>
       </c>
       <c r="T64" s="47" t="inlineStr">
@@ -8770,7 +8782,7 @@
       </c>
       <c r="S65" s="47" t="inlineStr">
         <is>
-          <t>ZB-A-ORDER-01</t>
+          <t>ZB-A-SHOP-01</t>
         </is>
       </c>
       <c r="T65" s="47" t="inlineStr">
